--- a/data/Simulasi Manual TA Rionaldo Fransiskus Silaen.xlsx
+++ b/data/Simulasi Manual TA Rionaldo Fransiskus Silaen.xlsx
@@ -5,22 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rionaldosilaen\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B427401-A167-4E89-9394-DF08641BC8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39000432-60D4-4267-8690-491474241FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="632" firstSheet="4" activeTab="7" xr2:uid="{51C07C40-CE71-4EF6-8E1B-C1439EB1384E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="632" xr2:uid="{51C07C40-CE71-4EF6-8E1B-C1439EB1384E}"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER DATA" sheetId="6" r:id="rId1"/>
-    <sheet name="IMPLEMENTASI MRP" sheetId="4" r:id="rId2"/>
-    <sheet name="IMPLEMENTASI PEMESANAN BARANG" sheetId="7" r:id="rId3"/>
-    <sheet name="IMPLEMENTASI QUALITY CONTROL" sheetId="2" r:id="rId4"/>
-    <sheet name="IMPLEMENTASI FIFO" sheetId="1" r:id="rId5"/>
-    <sheet name="ADMINISTRASI DEFECT" sheetId="3" r:id="rId6"/>
-    <sheet name="IMPLEMENTASI VPI" sheetId="5" r:id="rId7"/>
-    <sheet name="Dashboard" sheetId="9" r:id="rId8"/>
+    <sheet name="IMPLEMENTASI PEMESANAN BARANG" sheetId="7" r:id="rId1"/>
+    <sheet name="IMPLEMENTASI QUALITY CONTROL" sheetId="2" r:id="rId2"/>
+    <sheet name="IMPLEMENTASI FIFO" sheetId="1" r:id="rId3"/>
+    <sheet name="ADMINISTRASI DEFECT" sheetId="3" r:id="rId4"/>
+    <sheet name="IMPLEMENTASI VPI" sheetId="5" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="233">
   <si>
     <t>Tanggal</t>
   </si>
@@ -224,105 +222,9 @@
     <t>Total Hasil Akhir Return</t>
   </si>
   <si>
-    <t>MASTER PRODUCTION SCHEDULE (MPS)</t>
-  </si>
-  <si>
-    <t>Minggu 1</t>
-  </si>
-  <si>
-    <t>Minggu 2</t>
-  </si>
-  <si>
-    <t>Minggu 3</t>
-  </si>
-  <si>
-    <t>Satuan</t>
-  </si>
-  <si>
     <t>Keterangan</t>
   </si>
   <si>
-    <t>Demand / Pesanan (pcs)</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>Data permintaan / pesanan produksi</t>
-  </si>
-  <si>
-    <t>MPS / Produksi (pcs)</t>
-  </si>
-  <si>
-    <t>Rencana produksi = memenuhi demand</t>
-  </si>
-  <si>
-    <t>Keterangan / Rumus</t>
-  </si>
-  <si>
-    <t>GR</t>
-  </si>
-  <si>
-    <t>Gross Requirement
-(Kebutuhan Kotor)</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>GR = MPS × BOM = Produksi × 0,5 kg/pcs</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>Scheduled Receipts
-(Penerimaan Terjadwal)</t>
-  </si>
-  <si>
-    <t>PoH</t>
-  </si>
-  <si>
-    <t>Projected On Hand
-(Persediaan Awal Periode)</t>
-  </si>
-  <si>
-    <t>NR</t>
-  </si>
-  <si>
-    <t>Net Requirement
-(Kebutuhan Bersih)</t>
-  </si>
-  <si>
-    <t>PORt</t>
-  </si>
-  <si>
-    <t>Planned Order Receipt
-(Penerimaan Terencana)</t>
-  </si>
-  <si>
-    <t>PORel</t>
-  </si>
-  <si>
-    <t>Planned Order Release
-(Pelepasan Pesanan Terencana)</t>
-  </si>
-  <si>
-    <t>Minggu 4</t>
-  </si>
-  <si>
-    <t>Minggu 5</t>
-  </si>
-  <si>
-    <t>Minggu 6</t>
-  </si>
-  <si>
-    <t>Minggu 7</t>
-  </si>
-  <si>
-    <t>Minggu 0</t>
-  </si>
-  <si>
     <t>Quality</t>
   </si>
   <si>
@@ -450,9 +352,6 @@
   </si>
   <si>
     <t>DATA TOTAL PENGIRIMAN DELAY &amp; TEPAT WAKTU</t>
-  </si>
-  <si>
-    <t>MATERIAL REQUIREMENTS PLANNING (METODE LFL, LEAD TIME 1 MINGGU, DEFECT RATE 2.5%</t>
   </si>
   <si>
     <t>QUALITY CONTROL  DENGAN SNI AQL 2.5% DAN CHECKLIST 5 POINT INSPEKSI</t>
@@ -804,28 +703,6 @@
   </si>
   <si>
     <t xml:space="preserve">TAHAP 5: TEMPLATE PURCHASE ORDER &amp; QUALITY SPECIFICATION SHEET  </t>
-  </si>
-  <si>
-    <t>NR = GR - PoH − SR + SS, dengan syarat min 0</t>
-  </si>
-  <si>
-    <t>PORt M(t) = Jumlah barang yang masuk yang sudah direncanakan dengan LT = 1 minggu</t>
-  </si>
-  <si>
-    <t>SR =Bahan baku yang sudah di pesan/dijadwalkan tiba</t>
-  </si>
-  <si>
-    <t>PoH minggu ini = sisa stok minggu/periode kemarin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORel = NR (Lot-for-Lot); Pesanan yang dikirim ke supplier </t>
-  </si>
-  <si>
-    <t>PD</t>
-  </si>
-  <si>
-    <t>Komponen MRP
-LT: 1 minggu</t>
   </si>
   <si>
     <t>TAHAP 1: MENGIRIM TABEL RENCANA SAMPEL AQL 2,5</t>
@@ -877,7 +754,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -923,12 +800,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,12 +810,6 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1564,7 +1429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1630,15 +1495,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1668,7 +1524,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1711,7 +1567,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1731,22 +1587,265 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1761,295 +1860,52 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2064,91 +1920,70 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7054,487 +6889,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{848AAA2B-0F2D-45EC-BC54-8CD0590A1EC2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B39F936-292A-4B05-9A44-FDA761ECAFC0}">
-  <dimension ref="B1:M16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="8.7109375" style="23"/>
-    <col min="3" max="3" width="44.140625" style="23" customWidth="1"/>
-    <col min="4" max="6" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="23" customWidth="1"/>
-    <col min="8" max="11" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="23"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C2" s="76" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="78"/>
-    </row>
-    <row r="3" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="79"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="81"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="82" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="82"/>
-      <c r="D6" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="26">
-        <v>100</v>
-      </c>
-      <c r="E7" s="26">
-        <v>100</v>
-      </c>
-      <c r="F7" s="26">
-        <v>100</v>
-      </c>
-      <c r="G7" s="26">
-        <v>100</v>
-      </c>
-      <c r="H7" s="26">
-        <v>100</v>
-      </c>
-      <c r="I7" s="26">
-        <v>100</v>
-      </c>
-      <c r="J7" s="26">
-        <v>100</v>
-      </c>
-      <c r="K7" s="26">
-        <v>100</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="26">
-        <f t="shared" ref="D8:K8" si="0">D7</f>
-        <v>100</v>
-      </c>
-      <c r="E8" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F8" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="G8" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="H8" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I8" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="J8" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="K8" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="M8" s="27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="2:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="84" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9">
-        <f>E8*0.5</f>
-        <v>50</v>
-      </c>
-      <c r="F11" s="9">
-        <f t="shared" ref="F11:K11" si="1">F8*0.5</f>
-        <v>50</v>
-      </c>
-      <c r="G11" s="9">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="H11" s="9">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="J11" s="9">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="K11" s="9">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9">
-        <v>10</v>
-      </c>
-      <c r="F12" s="9">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="M12" s="27" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="9">
-        <v>20</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" ref="E13:K13" si="2">D13+E12+E15-E11</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="M13" s="27" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9">
-        <f t="shared" ref="E14:K14" si="3">MAX(0,E11-(D13+E12))</f>
-        <v>20</v>
-      </c>
-      <c r="F14" s="9">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="G14" s="9">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="H14" s="9">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="I14" s="9">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="J14" s="9">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="K14" s="9">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="M14" s="27" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9">
-        <f>D16</f>
-        <v>20</v>
-      </c>
-      <c r="F15" s="9">
-        <f>E16</f>
-        <v>50</v>
-      </c>
-      <c r="G15" s="9">
-        <f t="shared" ref="G15:K15" si="4">F16</f>
-        <v>50</v>
-      </c>
-      <c r="H15" s="9">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="I15" s="9">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="J15" s="9">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K15" s="9">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="L15" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="M15" s="27" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="9">
-        <f>E14</f>
-        <v>20</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" ref="E16:J16" si="5">F14</f>
-        <v>50</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="M16" s="27" t="s">
-        <v>253</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C2:L3"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B10:C10"/>
-  </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4B1EEE-8D2C-462F-98EF-DFD285E51E4E}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -7553,338 +6907,338 @@
   <sheetData>
     <row r="1" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C2" s="42"/>
-      <c r="D2" s="134" t="s">
-        <v>235</v>
-      </c>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="136"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="120" t="s">
+        <v>204</v>
+      </c>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="122"/>
     </row>
     <row r="3" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="42"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="139"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="125"/>
     </row>
     <row r="4" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D5" s="140" t="s">
-        <v>256</v>
-      </c>
-      <c r="E5" s="141"/>
-      <c r="F5" s="142"/>
+      <c r="D5" s="126" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" s="127"/>
+      <c r="F5" s="128"/>
     </row>
     <row r="6" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="143"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="145"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="131"/>
     </row>
     <row r="7" spans="2:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
     </row>
     <row r="8" spans="2:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C8" s="18" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="41">
+      <c r="E9" s="38">
         <v>2</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="38">
         <v>0</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="38">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="38">
+        <v>3</v>
+      </c>
+      <c r="F10" s="38">
+        <v>0</v>
+      </c>
+      <c r="G10" s="38">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C11" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="41">
+      <c r="E11" s="38">
+        <v>5</v>
+      </c>
+      <c r="F11" s="38">
+        <v>0</v>
+      </c>
+      <c r="G11" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C12" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="38">
+        <v>8</v>
+      </c>
+      <c r="F12" s="38">
+        <v>0</v>
+      </c>
+      <c r="G12" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="38">
+        <v>13</v>
+      </c>
+      <c r="F13" s="38">
+        <v>1</v>
+      </c>
+      <c r="G13" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C14" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="38">
+        <v>20</v>
+      </c>
+      <c r="F14" s="38">
+        <v>1</v>
+      </c>
+      <c r="G14" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="38">
+        <v>32</v>
+      </c>
+      <c r="F15" s="38">
+        <v>2</v>
+      </c>
+      <c r="G15" s="38">
         <v>3</v>
       </c>
-      <c r="F10" s="41">
-        <v>0</v>
-      </c>
-      <c r="G10" s="41">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" s="41">
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="38">
+        <v>50</v>
+      </c>
+      <c r="F16" s="38">
+        <v>3</v>
+      </c>
+      <c r="G16" s="38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C17" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="38">
+        <v>80</v>
+      </c>
+      <c r="F17" s="38">
         <v>5</v>
       </c>
-      <c r="F11" s="41">
-        <v>0</v>
-      </c>
-      <c r="G11" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="41">
+      <c r="G17" s="38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C18" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="38">
+        <v>125</v>
+      </c>
+      <c r="F18" s="38">
+        <v>7</v>
+      </c>
+      <c r="G18" s="38">
         <v>8</v>
       </c>
-      <c r="F12" s="41">
-        <v>0</v>
-      </c>
-      <c r="G12" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="41">
-        <v>13</v>
-      </c>
-      <c r="F13" s="41">
-        <v>1</v>
-      </c>
-      <c r="G13" s="41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="41">
-        <v>20</v>
-      </c>
-      <c r="F14" s="41">
-        <v>1</v>
-      </c>
-      <c r="G14" s="41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="41">
-        <v>32</v>
-      </c>
-      <c r="F15" s="41">
-        <v>2</v>
-      </c>
-      <c r="G15" s="41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" s="41">
-        <v>50</v>
-      </c>
-      <c r="F16" s="41">
-        <v>3</v>
-      </c>
-      <c r="G16" s="41">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="41" t="s">
+      <c r="I18" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="C19" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" s="41">
-        <v>80</v>
-      </c>
-      <c r="F17" s="41">
-        <v>5</v>
-      </c>
-      <c r="G17" s="41">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C18" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="41">
-        <v>125</v>
-      </c>
-      <c r="F18" s="41">
-        <v>7</v>
-      </c>
-      <c r="G18" s="41">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C19" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="41">
+      <c r="E19" s="38">
         <v>200</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="38">
         <v>10</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="38">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C23" s="140" t="s">
-        <v>247</v>
-      </c>
-      <c r="D23" s="141"/>
-      <c r="E23" s="142"/>
+      <c r="C23" s="126" t="s">
+        <v>216</v>
+      </c>
+      <c r="D23" s="127"/>
+      <c r="E23" s="128"/>
     </row>
     <row r="24" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="143"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="145"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="131"/>
     </row>
     <row r="26" spans="3:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C26" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="43" t="s">
-        <v>153</v>
+      <c r="C26" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="3:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C27" s="25" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="3:9" ht="63" x14ac:dyDescent="0.25">
       <c r="C28" s="25" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="3:9" ht="63" x14ac:dyDescent="0.25">
       <c r="C29" s="25" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.25">
@@ -7895,154 +7249,154 @@
     </row>
     <row r="32" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C33" s="140" t="s">
-        <v>257</v>
-      </c>
-      <c r="D33" s="141"/>
-      <c r="E33" s="142"/>
+      <c r="C33" s="126" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="127"/>
+      <c r="E33" s="128"/>
     </row>
     <row r="34" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="143"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="145"/>
+      <c r="C34" s="129"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="131"/>
     </row>
     <row r="35" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="D36" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>236</v>
+      <c r="C36" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="46" t="s">
-        <v>237</v>
-      </c>
-      <c r="D37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="E37" s="47" t="s">
-        <v>239</v>
+      <c r="C37" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="D38" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="E38" s="47" t="s">
-        <v>170</v>
+      <c r="C38" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="44" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="E39" s="47" t="s">
-        <v>173</v>
+      <c r="C39" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="D40" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="E40" s="47" t="s">
-        <v>223</v>
+      <c r="C40" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="44" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="D41" s="47" t="s">
+      <c r="C41" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="47" t="s">
-        <v>240</v>
+      <c r="E41" s="44" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="46" t="s">
+      <c r="C42" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="47" t="s">
-        <v>241</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>242</v>
+      <c r="D42" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="E42" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="D43" s="47">
+      <c r="C43" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" s="44">
         <v>0</v>
       </c>
-      <c r="E43" s="47" t="s">
-        <v>243</v>
+      <c r="E43" s="44" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="46" t="s">
-        <v>177</v>
-      </c>
-      <c r="D44" s="47">
+      <c r="C44" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="44">
         <v>1</v>
       </c>
-      <c r="E44" s="47" t="s">
-        <v>244</v>
+      <c r="E44" s="44" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="48" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D48" s="140" t="s">
-        <v>258</v>
-      </c>
-      <c r="E48" s="141"/>
-      <c r="F48" s="142"/>
+      <c r="D48" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E48" s="127"/>
+      <c r="F48" s="128"/>
     </row>
     <row r="49" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="143"/>
-      <c r="E49" s="144"/>
-      <c r="F49" s="145"/>
+      <c r="D49" s="129"/>
+      <c r="E49" s="130"/>
+      <c r="F49" s="131"/>
     </row>
     <row r="51" spans="3:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C51" s="24" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="G51" s="84" t="s">
-        <v>182</v>
-      </c>
-      <c r="H51" s="84"/>
+        <v>150</v>
+      </c>
+      <c r="G51" s="70" t="s">
+        <v>151</v>
+      </c>
+      <c r="H51" s="70"/>
     </row>
     <row r="52" spans="3:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C52" s="25" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="E52" s="25" t="s">
         <v>54</v>
@@ -8050,122 +7404,122 @@
       <c r="F52" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="G52" s="83" t="s">
-        <v>186</v>
-      </c>
-      <c r="H52" s="83"/>
+      <c r="G52" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="69"/>
     </row>
     <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="25" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="G53" s="83" t="s">
-        <v>191</v>
-      </c>
-      <c r="H53" s="83"/>
+        <v>159</v>
+      </c>
+      <c r="G53" s="69" t="s">
+        <v>160</v>
+      </c>
+      <c r="H53" s="69"/>
     </row>
     <row r="54" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C54" s="25" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="G54" s="83" t="s">
-        <v>196</v>
-      </c>
-      <c r="H54" s="83"/>
+        <v>164</v>
+      </c>
+      <c r="G54" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" s="69"/>
     </row>
     <row r="55" spans="3:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C55" s="25" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="G55" s="83" t="s">
-        <v>199</v>
-      </c>
-      <c r="H55" s="83"/>
+        <v>154</v>
+      </c>
+      <c r="G55" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="H55" s="69"/>
     </row>
     <row r="56" spans="3:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C56" s="25" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="G56" s="83" t="s">
-        <v>203</v>
-      </c>
-      <c r="H56" s="83"/>
+        <v>154</v>
+      </c>
+      <c r="G56" s="69" t="s">
+        <v>172</v>
+      </c>
+      <c r="H56" s="69"/>
     </row>
     <row r="57" spans="3:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C57" s="25" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="G57" s="83" t="s">
-        <v>206</v>
-      </c>
-      <c r="H57" s="83"/>
+        <v>154</v>
+      </c>
+      <c r="G57" s="69" t="s">
+        <v>175</v>
+      </c>
+      <c r="H57" s="69"/>
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="I60" s="2" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="D62" s="134" t="s">
-        <v>248</v>
-      </c>
-      <c r="E62" s="135"/>
-      <c r="F62" s="135"/>
-      <c r="G62" s="135"/>
-      <c r="H62" s="136"/>
+      <c r="D62" s="120" t="s">
+        <v>217</v>
+      </c>
+      <c r="E62" s="121"/>
+      <c r="F62" s="121"/>
+      <c r="G62" s="121"/>
+      <c r="H62" s="122"/>
     </row>
     <row r="63" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D63" s="137"/>
-      <c r="E63" s="138"/>
-      <c r="F63" s="138"/>
-      <c r="G63" s="138"/>
-      <c r="H63" s="139"/>
+      <c r="D63" s="123"/>
+      <c r="E63" s="124"/>
+      <c r="F63" s="124"/>
+      <c r="G63" s="124"/>
+      <c r="H63" s="125"/>
     </row>
     <row r="64" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C64" s="23"/>
@@ -8182,352 +7536,352 @@
       <c r="N64" s="23"/>
     </row>
     <row r="65" spans="3:9" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="128" t="s">
-        <v>207</v>
-      </c>
-      <c r="D65" s="129"/>
-      <c r="E65" s="129"/>
-      <c r="F65" s="129"/>
-      <c r="G65" s="129"/>
-      <c r="H65" s="129"/>
-      <c r="I65" s="130"/>
+      <c r="C65" s="114" t="s">
+        <v>176</v>
+      </c>
+      <c r="D65" s="115"/>
+      <c r="E65" s="115"/>
+      <c r="F65" s="115"/>
+      <c r="G65" s="115"/>
+      <c r="H65" s="115"/>
+      <c r="I65" s="116"/>
     </row>
     <row r="66" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C66" s="93" t="s">
-        <v>208</v>
-      </c>
-      <c r="D66" s="94"/>
-      <c r="E66" s="95"/>
-      <c r="F66" s="96" t="s">
-        <v>209</v>
-      </c>
-      <c r="G66" s="97"/>
-      <c r="H66" s="97"/>
-      <c r="I66" s="98"/>
+      <c r="C66" s="79" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" s="80"/>
+      <c r="E66" s="81"/>
+      <c r="F66" s="82" t="s">
+        <v>178</v>
+      </c>
+      <c r="G66" s="83"/>
+      <c r="H66" s="83"/>
+      <c r="I66" s="84"/>
     </row>
     <row r="67" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C67" s="85" t="s">
-        <v>210</v>
-      </c>
-      <c r="D67" s="86"/>
-      <c r="E67" s="87"/>
-      <c r="F67" s="99">
+      <c r="C67" s="71" t="s">
+        <v>179</v>
+      </c>
+      <c r="D67" s="72"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="85">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
-      </c>
-      <c r="G67" s="100"/>
-      <c r="H67" s="100"/>
-      <c r="I67" s="101"/>
+        <v>46219</v>
+      </c>
+      <c r="G67" s="86"/>
+      <c r="H67" s="86"/>
+      <c r="I67" s="87"/>
     </row>
     <row r="68" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C68" s="85" t="s">
+      <c r="C68" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="D68" s="86"/>
-      <c r="E68" s="87"/>
-      <c r="F68" s="88" t="s">
-        <v>211</v>
-      </c>
-      <c r="G68" s="89"/>
-      <c r="H68" s="89"/>
-      <c r="I68" s="90"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="74" t="s">
+        <v>180</v>
+      </c>
+      <c r="G68" s="75"/>
+      <c r="H68" s="75"/>
+      <c r="I68" s="76"/>
     </row>
     <row r="69" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="85" t="s">
-        <v>212</v>
-      </c>
-      <c r="D69" s="86"/>
-      <c r="E69" s="87"/>
-      <c r="F69" s="88" t="s">
-        <v>213</v>
-      </c>
-      <c r="G69" s="89"/>
-      <c r="H69" s="89"/>
-      <c r="I69" s="90"/>
+      <c r="C69" s="71" t="s">
+        <v>181</v>
+      </c>
+      <c r="D69" s="72"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="74" t="s">
+        <v>182</v>
+      </c>
+      <c r="G69" s="75"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="76"/>
     </row>
     <row r="70" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="85" t="s">
-        <v>214</v>
-      </c>
-      <c r="D70" s="86"/>
-      <c r="E70" s="87"/>
-      <c r="F70" s="91">
+      <c r="C70" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="D70" s="72"/>
+      <c r="E70" s="73"/>
+      <c r="F70" s="77">
         <v>15</v>
       </c>
-      <c r="G70" s="83"/>
-      <c r="H70" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="I70" s="92"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="I70" s="78"/>
     </row>
     <row r="71" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C71" s="85" t="s">
-        <v>216</v>
-      </c>
-      <c r="D71" s="86"/>
-      <c r="E71" s="87"/>
-      <c r="F71" s="91">
+      <c r="C71" s="71" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" s="72"/>
+      <c r="E71" s="73"/>
+      <c r="F71" s="77">
         <v>75000</v>
       </c>
-      <c r="G71" s="83"/>
-      <c r="H71" s="86" t="s">
-        <v>217</v>
-      </c>
-      <c r="I71" s="92"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="I71" s="78"/>
     </row>
     <row r="72" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="103" t="s">
-        <v>218</v>
-      </c>
-      <c r="D72" s="104"/>
-      <c r="E72" s="105"/>
-      <c r="F72" s="106">
+      <c r="C72" s="89" t="s">
+        <v>187</v>
+      </c>
+      <c r="D72" s="90"/>
+      <c r="E72" s="91"/>
+      <c r="F72" s="92">
         <f>F70*F71</f>
         <v>1125000</v>
       </c>
-      <c r="G72" s="107"/>
-      <c r="H72" s="107"/>
-      <c r="I72" s="108"/>
+      <c r="G72" s="93"/>
+      <c r="H72" s="93"/>
+      <c r="I72" s="94"/>
     </row>
     <row r="73" spans="3:9" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="128" t="s">
-        <v>219</v>
-      </c>
-      <c r="D73" s="129"/>
-      <c r="E73" s="129"/>
-      <c r="F73" s="129"/>
-      <c r="G73" s="129"/>
-      <c r="H73" s="129"/>
-      <c r="I73" s="130"/>
+      <c r="C73" s="114" t="s">
+        <v>188</v>
+      </c>
+      <c r="D73" s="115"/>
+      <c r="E73" s="115"/>
+      <c r="F73" s="115"/>
+      <c r="G73" s="115"/>
+      <c r="H73" s="115"/>
+      <c r="I73" s="116"/>
     </row>
     <row r="74" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C74" s="93" t="s">
-        <v>220</v>
-      </c>
-      <c r="D74" s="94"/>
-      <c r="E74" s="102"/>
-      <c r="F74" s="96" t="s">
-        <v>221</v>
-      </c>
-      <c r="G74" s="97"/>
-      <c r="H74" s="97"/>
-      <c r="I74" s="98"/>
+      <c r="C74" s="79" t="s">
+        <v>189</v>
+      </c>
+      <c r="D74" s="80"/>
+      <c r="E74" s="88"/>
+      <c r="F74" s="82" t="s">
+        <v>190</v>
+      </c>
+      <c r="G74" s="83"/>
+      <c r="H74" s="83"/>
+      <c r="I74" s="84"/>
     </row>
     <row r="75" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="85" t="s">
-        <v>175</v>
-      </c>
-      <c r="D75" s="86"/>
-      <c r="E75" s="92"/>
-      <c r="F75" s="88" t="s">
-        <v>222</v>
-      </c>
-      <c r="G75" s="89"/>
-      <c r="H75" s="89"/>
-      <c r="I75" s="90"/>
+      <c r="C75" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75" s="72"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="G75" s="75"/>
+      <c r="H75" s="75"/>
+      <c r="I75" s="76"/>
     </row>
     <row r="76" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C76" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="D76" s="86"/>
-      <c r="E76" s="92"/>
-      <c r="F76" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="G76" s="89"/>
-      <c r="H76" s="89"/>
-      <c r="I76" s="90"/>
+      <c r="C76" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="D76" s="72"/>
+      <c r="E76" s="78"/>
+      <c r="F76" s="74" t="s">
+        <v>193</v>
+      </c>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="76"/>
     </row>
     <row r="77" spans="3:9" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="103" t="s">
-        <v>225</v>
-      </c>
-      <c r="D77" s="104"/>
-      <c r="E77" s="127"/>
-      <c r="F77" s="131" t="str">
+      <c r="C77" s="89" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" s="90"/>
+      <c r="E77" s="113"/>
+      <c r="F77" s="117" t="str">
         <f>IF(F70&lt;=8,"Kode A: n=2, Ac=0, Re=1",IF(F70&lt;=15,"Kode B: n=3, Ac=0, Re=1",IF(F70&lt;=25,"Kode C: n=5, Ac=0, Re=1",IF(F70&lt;=50,"Kode D: n=8, Ac=0, Re=1",IF(F70&lt;=90,"Kode E: n=13, Ac=1, Re=2",IF(F70&lt;=150,"Kode F: n=20, Ac=1, Re=2",IF(F70&lt;=280,"Kode G: n=32, Ac=2, Re=3",IF(F70&lt;=500,"Kode H: n=50, Ac=3, Re=4",IF(F70&lt;=1200,"Kode J: n=80, Ac=5, Re=6",IF(F70&lt;=3200,"Kode K: n=125, Ac=7, Re=8","Kode L: n=200, Ac=10, Re=11"))))))))))</f>
         <v>Kode B: n=3, Ac=0, Re=1</v>
       </c>
-      <c r="G77" s="132"/>
-      <c r="H77" s="132"/>
-      <c r="I77" s="133"/>
+      <c r="G77" s="118"/>
+      <c r="H77" s="118"/>
+      <c r="I77" s="119"/>
     </row>
     <row r="78" spans="3:9" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="128" t="s">
-        <v>226</v>
-      </c>
-      <c r="D78" s="129"/>
-      <c r="E78" s="129"/>
-      <c r="F78" s="129"/>
-      <c r="G78" s="129"/>
-      <c r="H78" s="129"/>
-      <c r="I78" s="130"/>
+      <c r="C78" s="114" t="s">
+        <v>195</v>
+      </c>
+      <c r="D78" s="115"/>
+      <c r="E78" s="115"/>
+      <c r="F78" s="115"/>
+      <c r="G78" s="115"/>
+      <c r="H78" s="115"/>
+      <c r="I78" s="116"/>
     </row>
     <row r="79" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C79" s="93" t="s">
-        <v>187</v>
-      </c>
-      <c r="D79" s="94"/>
-      <c r="E79" s="102"/>
-      <c r="F79" s="93" t="s">
-        <v>227</v>
-      </c>
-      <c r="G79" s="102"/>
-      <c r="H79" s="93" t="s">
-        <v>228</v>
-      </c>
-      <c r="I79" s="102"/>
+      <c r="C79" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="D79" s="80"/>
+      <c r="E79" s="88"/>
+      <c r="F79" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="G79" s="88"/>
+      <c r="H79" s="79" t="s">
+        <v>197</v>
+      </c>
+      <c r="I79" s="88"/>
     </row>
     <row r="80" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C80" s="85" t="s">
-        <v>192</v>
-      </c>
-      <c r="D80" s="86"/>
-      <c r="E80" s="92"/>
-      <c r="F80" s="85" t="s">
-        <v>229</v>
-      </c>
-      <c r="G80" s="92"/>
-      <c r="H80" s="85" t="s">
-        <v>230</v>
-      </c>
-      <c r="I80" s="92"/>
+      <c r="C80" s="71" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" s="72"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="G80" s="78"/>
+      <c r="H80" s="71" t="s">
+        <v>199</v>
+      </c>
+      <c r="I80" s="78"/>
     </row>
     <row r="81" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C81" s="85" t="s">
-        <v>197</v>
-      </c>
-      <c r="D81" s="86"/>
-      <c r="E81" s="92"/>
-      <c r="F81" s="85" t="s">
-        <v>198</v>
-      </c>
-      <c r="G81" s="92"/>
-      <c r="H81" s="85" t="s">
-        <v>231</v>
-      </c>
-      <c r="I81" s="92"/>
+      <c r="C81" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" s="72"/>
+      <c r="E81" s="78"/>
+      <c r="F81" s="71" t="s">
+        <v>167</v>
+      </c>
+      <c r="G81" s="78"/>
+      <c r="H81" s="71" t="s">
+        <v>200</v>
+      </c>
+      <c r="I81" s="78"/>
     </row>
     <row r="82" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C82" s="103" t="s">
-        <v>204</v>
-      </c>
-      <c r="D82" s="104"/>
-      <c r="E82" s="127"/>
-      <c r="F82" s="103" t="s">
-        <v>232</v>
-      </c>
-      <c r="G82" s="127"/>
-      <c r="H82" s="103" t="s">
-        <v>233</v>
-      </c>
-      <c r="I82" s="127"/>
+      <c r="C82" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="D82" s="90"/>
+      <c r="E82" s="113"/>
+      <c r="F82" s="89" t="s">
+        <v>201</v>
+      </c>
+      <c r="G82" s="113"/>
+      <c r="H82" s="89" t="s">
+        <v>202</v>
+      </c>
+      <c r="I82" s="113"/>
     </row>
     <row r="83" spans="3:14" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C83" s="128" t="s">
-        <v>234</v>
-      </c>
-      <c r="D83" s="129"/>
-      <c r="E83" s="129"/>
-      <c r="F83" s="129"/>
-      <c r="G83" s="129"/>
-      <c r="H83" s="129"/>
-      <c r="I83" s="130"/>
+      <c r="C83" s="114" t="s">
+        <v>203</v>
+      </c>
+      <c r="D83" s="115"/>
+      <c r="E83" s="115"/>
+      <c r="F83" s="115"/>
+      <c r="G83" s="115"/>
+      <c r="H83" s="115"/>
+      <c r="I83" s="116"/>
     </row>
     <row r="84" spans="3:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C84" s="109" t="s">
-        <v>245</v>
-      </c>
-      <c r="D84" s="110"/>
-      <c r="E84" s="111"/>
-      <c r="F84" s="118" t="s">
-        <v>246</v>
-      </c>
-      <c r="G84" s="119"/>
-      <c r="H84" s="119"/>
-      <c r="I84" s="120"/>
+      <c r="C84" s="95" t="s">
+        <v>214</v>
+      </c>
+      <c r="D84" s="96"/>
+      <c r="E84" s="97"/>
+      <c r="F84" s="104" t="s">
+        <v>215</v>
+      </c>
+      <c r="G84" s="105"/>
+      <c r="H84" s="105"/>
+      <c r="I84" s="106"/>
     </row>
     <row r="85" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C85" s="112"/>
-      <c r="D85" s="113"/>
-      <c r="E85" s="114"/>
-      <c r="F85" s="121"/>
-      <c r="G85" s="122"/>
-      <c r="H85" s="122"/>
-      <c r="I85" s="123"/>
+      <c r="C85" s="98"/>
+      <c r="D85" s="99"/>
+      <c r="E85" s="100"/>
+      <c r="F85" s="107"/>
+      <c r="G85" s="108"/>
+      <c r="H85" s="108"/>
+      <c r="I85" s="109"/>
     </row>
     <row r="86" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C86" s="112"/>
-      <c r="D86" s="113"/>
-      <c r="E86" s="114"/>
-      <c r="F86" s="121"/>
-      <c r="G86" s="122"/>
-      <c r="H86" s="122"/>
-      <c r="I86" s="123"/>
+      <c r="C86" s="98"/>
+      <c r="D86" s="99"/>
+      <c r="E86" s="100"/>
+      <c r="F86" s="107"/>
+      <c r="G86" s="108"/>
+      <c r="H86" s="108"/>
+      <c r="I86" s="109"/>
     </row>
     <row r="87" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C87" s="112"/>
-      <c r="D87" s="113"/>
-      <c r="E87" s="114"/>
-      <c r="F87" s="121"/>
-      <c r="G87" s="122"/>
-      <c r="H87" s="122"/>
-      <c r="I87" s="123"/>
+      <c r="C87" s="98"/>
+      <c r="D87" s="99"/>
+      <c r="E87" s="100"/>
+      <c r="F87" s="107"/>
+      <c r="G87" s="108"/>
+      <c r="H87" s="108"/>
+      <c r="I87" s="109"/>
     </row>
     <row r="88" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C88" s="112"/>
-      <c r="D88" s="113"/>
-      <c r="E88" s="114"/>
-      <c r="F88" s="121"/>
-      <c r="G88" s="122"/>
-      <c r="H88" s="122"/>
-      <c r="I88" s="123"/>
+      <c r="C88" s="98"/>
+      <c r="D88" s="99"/>
+      <c r="E88" s="100"/>
+      <c r="F88" s="107"/>
+      <c r="G88" s="108"/>
+      <c r="H88" s="108"/>
+      <c r="I88" s="109"/>
     </row>
     <row r="89" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C89" s="112"/>
-      <c r="D89" s="113"/>
-      <c r="E89" s="114"/>
-      <c r="F89" s="121"/>
-      <c r="G89" s="122"/>
-      <c r="H89" s="122"/>
-      <c r="I89" s="123"/>
+      <c r="C89" s="98"/>
+      <c r="D89" s="99"/>
+      <c r="E89" s="100"/>
+      <c r="F89" s="107"/>
+      <c r="G89" s="108"/>
+      <c r="H89" s="108"/>
+      <c r="I89" s="109"/>
     </row>
     <row r="90" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C90" s="112"/>
-      <c r="D90" s="113"/>
-      <c r="E90" s="114"/>
-      <c r="F90" s="121"/>
-      <c r="G90" s="122"/>
-      <c r="H90" s="122"/>
-      <c r="I90" s="123"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="99"/>
+      <c r="E90" s="100"/>
+      <c r="F90" s="107"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="108"/>
+      <c r="I90" s="109"/>
     </row>
     <row r="91" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C91" s="112"/>
-      <c r="D91" s="113"/>
-      <c r="E91" s="114"/>
-      <c r="F91" s="121"/>
-      <c r="G91" s="122"/>
-      <c r="H91" s="122"/>
-      <c r="I91" s="123"/>
+      <c r="C91" s="98"/>
+      <c r="D91" s="99"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="107"/>
+      <c r="G91" s="108"/>
+      <c r="H91" s="108"/>
+      <c r="I91" s="109"/>
     </row>
     <row r="92" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C92" s="112"/>
-      <c r="D92" s="113"/>
-      <c r="E92" s="114"/>
-      <c r="F92" s="121"/>
-      <c r="G92" s="122"/>
-      <c r="H92" s="122"/>
-      <c r="I92" s="123"/>
+      <c r="C92" s="98"/>
+      <c r="D92" s="99"/>
+      <c r="E92" s="100"/>
+      <c r="F92" s="107"/>
+      <c r="G92" s="108"/>
+      <c r="H92" s="108"/>
+      <c r="I92" s="109"/>
     </row>
     <row r="93" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C93" s="115"/>
-      <c r="D93" s="116"/>
-      <c r="E93" s="117"/>
-      <c r="F93" s="124"/>
-      <c r="G93" s="125"/>
-      <c r="H93" s="125"/>
-      <c r="I93" s="126"/>
+      <c r="C93" s="101"/>
+      <c r="D93" s="102"/>
+      <c r="E93" s="103"/>
+      <c r="F93" s="110"/>
+      <c r="G93" s="111"/>
+      <c r="H93" s="111"/>
+      <c r="I93" s="112"/>
       <c r="J93" s="23"/>
       <c r="K93" s="23"/>
       <c r="L93" s="23"/>
@@ -8610,7 +7964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13887B3D-ABA6-40F5-9562-D7EADADD5B53}">
   <dimension ref="B1:AH40"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -8651,30 +8005,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="F1" s="146" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="148"/>
+      <c r="F1" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="65"/>
     </row>
     <row r="2" spans="2:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2" s="149"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="150"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="150"/>
-      <c r="M2" s="150"/>
-      <c r="N2" s="150"/>
-      <c r="O2" s="151"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="68"/>
     </row>
     <row r="4" spans="2:34" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -8725,17 +8079,17 @@
       <c r="Q4" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="S4" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="T4" s="39" t="s">
-        <v>124</v>
+      <c r="R4" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="T4" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.25">
@@ -8758,7 +8112,7 @@
         <v>8</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I29" si="0">IF(H5="","",IFERROR(VLOOKUP(H5,$AD$6:$AF$17,2,0),"?"))</f>
@@ -8768,7 +8122,7 @@
         <f t="shared" ref="J5:J29" si="1">IF(H5="","",IFERROR(VLOOKUP(H5,$AD$6:$AF$17,3,0),"?"))</f>
         <v>2</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="45">
         <v>1</v>
       </c>
       <c r="L5" s="9" t="s">
@@ -8791,7 +8145,7 @@
         <v>51</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="S5" s="1" t="str">
         <f>C5</f>
@@ -8824,7 +8178,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
@@ -8834,7 +8188,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="45">
         <v>0</v>
       </c>
       <c r="L6" s="9" t="s">
@@ -8857,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="S6" s="1" t="str">
         <f>C6</f>
@@ -8869,15 +8223,15 @@
       </c>
       <c r="U6" s="1"/>
       <c r="Z6" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA6" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA6" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AB6" s="34" t="s">
+      <c r="AB6" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="AC6" s="34" t="s">
+      <c r="AC6" s="31" t="s">
         <v>3</v>
       </c>
       <c r="AD6" s="14" t="s">
@@ -8889,10 +8243,10 @@
       <c r="AF6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="AG6" s="35" t="s">
+      <c r="AG6" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="AH6" s="35" t="s">
+      <c r="AH6" s="32" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8917,7 +8271,7 @@
         <v>20</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="0"/>
@@ -8927,7 +8281,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="45">
         <v>2</v>
       </c>
       <c r="L7" s="9" t="s">
@@ -8950,7 +8304,7 @@
         <v>51</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="S7" s="1" t="str">
         <f t="shared" ref="S7:S10" si="5">C7</f>
@@ -8962,19 +8316,19 @@
       </c>
       <c r="U7" s="1"/>
       <c r="Z7" s="15" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="AA7" s="15">
         <v>2</v>
       </c>
-      <c r="AB7" s="33" t="s">
+      <c r="AB7" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="AC7" s="33" t="s">
+      <c r="AC7" s="30" t="s">
         <v>10</v>
       </c>
       <c r="AD7" s="15" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AE7" s="15">
         <v>0</v>
@@ -9008,7 +8362,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="0"/>
@@ -9018,7 +8372,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K8" s="48">
+      <c r="K8" s="45">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="s">
@@ -9053,15 +8407,15 @@
       </c>
       <c r="U8" s="1"/>
       <c r="Z8" s="15" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="AA8" s="15">
         <v>3</v>
       </c>
-      <c r="AB8" s="33" t="s">
+      <c r="AB8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AC8" s="33" t="s">
+      <c r="AC8" s="30" t="s">
         <v>11</v>
       </c>
       <c r="AD8" s="15" t="s">
@@ -9099,7 +8453,7 @@
         <v>50</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="0"/>
@@ -9109,7 +8463,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K9" s="48">
+      <c r="K9" s="45">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -9144,19 +8498,19 @@
       </c>
       <c r="U9" s="1"/>
       <c r="Z9" s="15" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="AA9" s="15">
         <v>5</v>
       </c>
-      <c r="AB9" s="33" t="s">
+      <c r="AB9" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AC9" s="30" t="s">
         <v>13</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="AE9" s="15">
         <v>0</v>
@@ -9198,7 +8552,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K10" s="48">
+      <c r="K10" s="45">
         <v>20</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -9233,7 +8587,7 @@
       </c>
       <c r="U10" s="1"/>
       <c r="Z10" s="15" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AA10" s="15">
         <v>8</v>
@@ -9241,7 +8595,7 @@
       <c r="AB10" s="20"/>
       <c r="AC10" s="20"/>
       <c r="AD10" s="15" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="AE10" s="15">
         <v>0</v>
@@ -9253,40 +8607,40 @@
       <c r="AH10" s="20"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B11" s="49">
+      <c r="B11" s="46">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49" t="str">
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J11" s="49" t="str">
+      <c r="J11" s="46" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K11" s="49"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="50" t="str">
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="47" t="str">
         <f t="shared" ref="M11:M29" si="6">IF(K11="","",IF(K11&lt;=I11,"LOLOS",IF(K11&gt;=J11,"RETUR","HOLD")))</f>
         <v/>
       </c>
-      <c r="N11" s="49"/>
-      <c r="O11" s="49"/>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
       <c r="Z11" s="15" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="AA11" s="15">
         <v>13</v>
@@ -9294,7 +8648,7 @@
       <c r="AB11" s="20"/>
       <c r="AC11" s="20"/>
       <c r="AD11" s="15" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="AE11" s="15">
         <v>1</v>
@@ -9339,7 +8693,7 @@
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="Z12" s="15" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="AA12" s="15">
         <v>20</v>
@@ -9347,7 +8701,7 @@
       <c r="AB12" s="20"/>
       <c r="AC12" s="20"/>
       <c r="AD12" s="15" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="AE12" s="15">
         <v>1</v>
@@ -9392,7 +8746,7 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="Z13" s="15" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="AA13" s="15">
         <v>32</v>
@@ -9445,7 +8799,7 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="Z14" s="15" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="AA14" s="15">
         <v>50</v>
@@ -9453,7 +8807,7 @@
       <c r="AB14" s="20"/>
       <c r="AC14" s="20"/>
       <c r="AD14" s="15" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AE14" s="15">
         <v>3</v>
@@ -9498,7 +8852,7 @@
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="Z15" s="15" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="AA15" s="15">
         <v>80</v>
@@ -9506,7 +8860,7 @@
       <c r="AB15" s="20"/>
       <c r="AC15" s="20"/>
       <c r="AD15" s="15" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="AE15" s="15">
         <v>5</v>
@@ -9551,7 +8905,7 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="Z16" s="15" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="15">
         <v>125</v>
@@ -9559,7 +8913,7 @@
       <c r="AB16" s="20"/>
       <c r="AC16" s="20"/>
       <c r="AD16" s="15" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AE16" s="15">
         <v>7</v>
@@ -9604,7 +8958,7 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="Z17" s="15" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="AA17" s="15">
         <v>200</v>
@@ -9612,7 +8966,7 @@
       <c r="AB17" s="20"/>
       <c r="AC17" s="20"/>
       <c r="AD17" s="15" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AE17" s="15">
         <v>10</v>
@@ -10063,7 +9417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1534881D-0B0F-41D5-9E46-78590B8DAFDD}">
   <dimension ref="B1:O23"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -10091,26 +9445,26 @@
   <sheetData>
     <row r="1" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="146" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="148"/>
+      <c r="D2" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="65"/>
     </row>
     <row r="3" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="149"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="151"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="68"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
@@ -10437,7 +9791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F014A1-179D-4536-955C-726FEFEB8065}">
   <dimension ref="B2:N9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -10460,31 +9814,31 @@
   <sheetData>
     <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="38"/>
-      <c r="C3" s="152" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
-      <c r="F3" s="153"/>
-      <c r="G3" s="154"/>
-      <c r="K3" s="158" t="s">
-        <v>132</v>
-      </c>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="132" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="134"/>
+      <c r="K3" s="138" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="139"/>
+      <c r="M3" s="139"/>
+      <c r="N3" s="140"/>
     </row>
     <row r="4" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="155"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="157"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="163"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="137"/>
+      <c r="K4" s="141"/>
+      <c r="L4" s="142"/>
+      <c r="M4" s="142"/>
+      <c r="N4" s="143"/>
     </row>
     <row r="6" spans="2:14" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
@@ -10494,7 +9848,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E6" s="24" t="s">
         <v>55</v>
@@ -10511,14 +9865,14 @@
       <c r="K6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="M6" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="N6" s="39" t="s">
-        <v>131</v>
+      <c r="L6" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="M6" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="N6" s="36" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -10659,60 +10013,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3423FA21-9284-4F38-879B-2539DE9C91F3}">
   <dimension ref="D3:L25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="30"/>
-    <col min="2" max="2" width="17.85546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" style="30" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="30" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="30"/>
-    <col min="13" max="13" width="9" style="30" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="30"/>
+    <col min="1" max="1" width="8.7109375" style="27"/>
+    <col min="2" max="2" width="17.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="27"/>
+    <col min="13" max="13" width="9" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="27"/>
   </cols>
   <sheetData>
     <row r="3" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="E4" s="66" t="s">
-        <v>137</v>
-      </c>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="68"/>
+      <c r="E4" s="144" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="146"/>
     </row>
     <row r="5" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="69"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="71"/>
+      <c r="E5" s="147"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="149"/>
     </row>
     <row r="7" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>99</v>
+      <c r="E7" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="4:9" x14ac:dyDescent="0.25">
@@ -10727,15 +10081,15 @@
         <f>'ADMINISTRASI DEFECT'!H7</f>
         <v>1</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="33">
         <f>'ADMINISTRASI DEFECT'!L7</f>
         <v>2</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="33">
         <f>'ADMINISTRASI DEFECT'!N7</f>
         <v>2</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="34">
         <v>75</v>
       </c>
     </row>
@@ -10751,15 +10105,15 @@
         <f>'ADMINISTRASI DEFECT'!H8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="33">
         <f>'ADMINISTRASI DEFECT'!M8</f>
         <v>1</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="33">
         <f>'ADMINISTRASI DEFECT'!N8</f>
         <v>1</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="34">
         <v>73</v>
       </c>
     </row>
@@ -10775,63 +10129,63 @@
         <f>'ADMINISTRASI DEFECT'!H9</f>
         <v>2</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="33">
         <f>'ADMINISTRASI DEFECT'!M9</f>
         <v>2</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="33">
         <f>'ADMINISTRASI DEFECT'!N9</f>
         <v>0</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="34">
         <v>72</v>
       </c>
     </row>
     <row r="18" spans="4:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="68"/>
-      <c r="K19" s="72" t="s">
-        <v>138</v>
-      </c>
-      <c r="L19" s="73"/>
+      <c r="E19" s="144" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="145"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="146"/>
+      <c r="K19" s="150" t="s">
+        <v>107</v>
+      </c>
+      <c r="L19" s="151"/>
     </row>
     <row r="20" spans="4:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="69"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="71"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="75"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="148"/>
+      <c r="G20" s="148"/>
+      <c r="H20" s="149"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="153"/>
     </row>
     <row r="22" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D22" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="K22" s="9" t="str">
         <f>E22</f>
         <v>Quality</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="29">
         <v>0.5</v>
       </c>
     </row>
@@ -10840,7 +10194,7 @@
         <f>D8</f>
         <v>Vendor A</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="37">
         <f>((E8-F8)/E8)*100</f>
         <v>50</v>
       </c>
@@ -10864,7 +10218,7 @@
         <f>F22</f>
         <v>Delivery</v>
       </c>
-      <c r="L23" s="32">
+      <c r="L23" s="29">
         <v>0.3</v>
       </c>
     </row>
@@ -10873,7 +10227,7 @@
         <f>D9</f>
         <v>Vendor B</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="37">
         <f>((E9-F9)/E9)*100</f>
         <v>100</v>
       </c>
@@ -10881,11 +10235,11 @@
         <f>((H9/G9)*100)</f>
         <v>100</v>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="37">
         <f>((I10/I9)*100)</f>
         <v>98.630136986301366</v>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="37">
         <f>(E24*L22)+(F24*L23)+(G24*L24)</f>
         <v>99.726027397260282</v>
       </c>
@@ -10897,7 +10251,7 @@
         <f>G22</f>
         <v>Price</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="29">
         <v>0.2</v>
       </c>
     </row>
@@ -10906,7 +10260,7 @@
         <f>D10</f>
         <v>Vendor C</v>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="37">
         <f>((E10-F10)/E10)*100</f>
         <v>0</v>
       </c>
@@ -10937,7 +10291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFF980D-7AE5-429A-849F-FA28295604D6}">
   <dimension ref="E4:BU121"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -10962,282 +10316,282 @@
   <sheetData>
     <row r="4" spans="5:38" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="K5" s="164" t="s">
-        <v>270</v>
-      </c>
-      <c r="L5" s="165"/>
-      <c r="M5" s="165"/>
-      <c r="N5" s="165"/>
-      <c r="O5" s="165"/>
-      <c r="P5" s="165"/>
-      <c r="Q5" s="165"/>
-      <c r="R5" s="165"/>
-      <c r="S5" s="165"/>
-      <c r="T5" s="165"/>
-      <c r="U5" s="165"/>
-      <c r="V5" s="165"/>
-      <c r="W5" s="165"/>
-      <c r="X5" s="165"/>
-      <c r="Y5" s="165"/>
-      <c r="Z5" s="165"/>
-      <c r="AA5" s="165"/>
-      <c r="AB5" s="165"/>
-      <c r="AC5" s="165"/>
-      <c r="AD5" s="166"/>
+      <c r="K5" s="161" t="s">
+        <v>232</v>
+      </c>
+      <c r="L5" s="162"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="162"/>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="162"/>
+      <c r="R5" s="162"/>
+      <c r="S5" s="162"/>
+      <c r="T5" s="162"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="162"/>
+      <c r="W5" s="162"/>
+      <c r="X5" s="162"/>
+      <c r="Y5" s="162"/>
+      <c r="Z5" s="162"/>
+      <c r="AA5" s="162"/>
+      <c r="AB5" s="162"/>
+      <c r="AC5" s="162"/>
+      <c r="AD5" s="163"/>
     </row>
     <row r="6" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="K6" s="167"/>
-      <c r="L6" s="168"/>
-      <c r="M6" s="168"/>
-      <c r="N6" s="168"/>
-      <c r="O6" s="168"/>
-      <c r="P6" s="168"/>
-      <c r="Q6" s="168"/>
-      <c r="R6" s="168"/>
-      <c r="S6" s="168"/>
-      <c r="T6" s="168"/>
-      <c r="U6" s="168"/>
-      <c r="V6" s="168"/>
-      <c r="W6" s="168"/>
-      <c r="X6" s="168"/>
-      <c r="Y6" s="168"/>
-      <c r="Z6" s="168"/>
-      <c r="AA6" s="168"/>
-      <c r="AB6" s="168"/>
-      <c r="AC6" s="168"/>
-      <c r="AD6" s="169"/>
+      <c r="K6" s="164"/>
+      <c r="L6" s="165"/>
+      <c r="M6" s="165"/>
+      <c r="N6" s="165"/>
+      <c r="O6" s="165"/>
+      <c r="P6" s="165"/>
+      <c r="Q6" s="165"/>
+      <c r="R6" s="165"/>
+      <c r="S6" s="165"/>
+      <c r="T6" s="165"/>
+      <c r="U6" s="165"/>
+      <c r="V6" s="165"/>
+      <c r="W6" s="165"/>
+      <c r="X6" s="165"/>
+      <c r="Y6" s="165"/>
+      <c r="Z6" s="165"/>
+      <c r="AA6" s="165"/>
+      <c r="AB6" s="165"/>
+      <c r="AC6" s="165"/>
+      <c r="AD6" s="166"/>
     </row>
     <row r="7" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="K7" s="167"/>
-      <c r="L7" s="168"/>
-      <c r="M7" s="168"/>
-      <c r="N7" s="168"/>
-      <c r="O7" s="168"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="168"/>
-      <c r="R7" s="168"/>
-      <c r="S7" s="168"/>
-      <c r="T7" s="168"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="168"/>
-      <c r="W7" s="168"/>
-      <c r="X7" s="168"/>
-      <c r="Y7" s="168"/>
-      <c r="Z7" s="168"/>
-      <c r="AA7" s="168"/>
-      <c r="AB7" s="168"/>
-      <c r="AC7" s="168"/>
-      <c r="AD7" s="169"/>
+      <c r="K7" s="164"/>
+      <c r="L7" s="165"/>
+      <c r="M7" s="165"/>
+      <c r="N7" s="165"/>
+      <c r="O7" s="165"/>
+      <c r="P7" s="165"/>
+      <c r="Q7" s="165"/>
+      <c r="R7" s="165"/>
+      <c r="S7" s="165"/>
+      <c r="T7" s="165"/>
+      <c r="U7" s="165"/>
+      <c r="V7" s="165"/>
+      <c r="W7" s="165"/>
+      <c r="X7" s="165"/>
+      <c r="Y7" s="165"/>
+      <c r="Z7" s="165"/>
+      <c r="AA7" s="165"/>
+      <c r="AB7" s="165"/>
+      <c r="AC7" s="165"/>
+      <c r="AD7" s="166"/>
     </row>
     <row r="8" spans="5:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K8" s="167"/>
-      <c r="L8" s="168"/>
-      <c r="M8" s="168"/>
-      <c r="N8" s="168"/>
-      <c r="O8" s="168"/>
-      <c r="P8" s="168"/>
-      <c r="Q8" s="168"/>
-      <c r="R8" s="168"/>
-      <c r="S8" s="168"/>
-      <c r="T8" s="168"/>
-      <c r="U8" s="168"/>
-      <c r="V8" s="168"/>
-      <c r="W8" s="168"/>
-      <c r="X8" s="168"/>
-      <c r="Y8" s="168"/>
-      <c r="Z8" s="168"/>
-      <c r="AA8" s="168"/>
-      <c r="AB8" s="168"/>
-      <c r="AC8" s="168"/>
-      <c r="AD8" s="169"/>
+      <c r="K8" s="164"/>
+      <c r="L8" s="165"/>
+      <c r="M8" s="165"/>
+      <c r="N8" s="165"/>
+      <c r="O8" s="165"/>
+      <c r="P8" s="165"/>
+      <c r="Q8" s="165"/>
+      <c r="R8" s="165"/>
+      <c r="S8" s="165"/>
+      <c r="T8" s="165"/>
+      <c r="U8" s="165"/>
+      <c r="V8" s="165"/>
+      <c r="W8" s="165"/>
+      <c r="X8" s="165"/>
+      <c r="Y8" s="165"/>
+      <c r="Z8" s="165"/>
+      <c r="AA8" s="165"/>
+      <c r="AB8" s="165"/>
+      <c r="AC8" s="165"/>
+      <c r="AD8" s="166"/>
     </row>
     <row r="9" spans="5:38" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K9" s="170"/>
-      <c r="L9" s="171"/>
-      <c r="M9" s="171"/>
-      <c r="N9" s="171"/>
-      <c r="O9" s="171"/>
-      <c r="P9" s="171"/>
-      <c r="Q9" s="171"/>
-      <c r="R9" s="171"/>
-      <c r="S9" s="171"/>
-      <c r="T9" s="171"/>
-      <c r="U9" s="171"/>
-      <c r="V9" s="171"/>
-      <c r="W9" s="171"/>
-      <c r="X9" s="171"/>
-      <c r="Y9" s="171"/>
-      <c r="Z9" s="171"/>
-      <c r="AA9" s="171"/>
-      <c r="AB9" s="171"/>
-      <c r="AC9" s="171"/>
-      <c r="AD9" s="172"/>
+      <c r="K9" s="167"/>
+      <c r="L9" s="168"/>
+      <c r="M9" s="168"/>
+      <c r="N9" s="168"/>
+      <c r="O9" s="168"/>
+      <c r="P9" s="168"/>
+      <c r="Q9" s="168"/>
+      <c r="R9" s="168"/>
+      <c r="S9" s="168"/>
+      <c r="T9" s="168"/>
+      <c r="U9" s="168"/>
+      <c r="V9" s="168"/>
+      <c r="W9" s="168"/>
+      <c r="X9" s="168"/>
+      <c r="Y9" s="168"/>
+      <c r="Z9" s="168"/>
+      <c r="AA9" s="168"/>
+      <c r="AB9" s="168"/>
+      <c r="AC9" s="168"/>
+      <c r="AD9" s="169"/>
     </row>
     <row r="12" spans="5:38" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="5:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="58"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="59"/>
-      <c r="N13" s="59"/>
-      <c r="O13" s="59"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="59"/>
-      <c r="S13" s="59"/>
-      <c r="T13" s="59"/>
-      <c r="U13" s="59"/>
-      <c r="V13" s="59"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="59"/>
-      <c r="Y13" s="59"/>
-      <c r="Z13" s="59"/>
-      <c r="AA13" s="59"/>
-      <c r="AB13" s="59"/>
-      <c r="AC13" s="59"/>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="59"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="59"/>
-      <c r="AH13" s="59"/>
-      <c r="AI13" s="59"/>
-      <c r="AJ13" s="59"/>
-      <c r="AK13" s="59"/>
-      <c r="AL13" s="60"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="56"/>
+      <c r="V13" s="56"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="56"/>
+      <c r="Y13" s="56"/>
+      <c r="Z13" s="56"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="56"/>
+      <c r="AC13" s="56"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="56"/>
+      <c r="AH13" s="56"/>
+      <c r="AI13" s="56"/>
+      <c r="AJ13" s="56"/>
+      <c r="AK13" s="56"/>
+      <c r="AL13" s="57"/>
     </row>
     <row r="14" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E14" s="61"/>
-      <c r="AL14" s="62"/>
+      <c r="E14" s="58"/>
+      <c r="AL14" s="59"/>
     </row>
     <row r="15" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E15" s="61"/>
-      <c r="AL15" s="62"/>
+      <c r="E15" s="58"/>
+      <c r="AL15" s="59"/>
     </row>
     <row r="16" spans="5:38" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E16" s="61"/>
-      <c r="AL16" s="62"/>
+      <c r="E16" s="58"/>
+      <c r="AL16" s="59"/>
     </row>
     <row r="17" spans="5:71" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="61"/>
-      <c r="H17" s="177" t="s">
-        <v>268</v>
-      </c>
-      <c r="I17" s="178"/>
-      <c r="J17" s="178"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="178"/>
-      <c r="M17" s="178"/>
-      <c r="N17" s="179"/>
-      <c r="Q17" s="177" t="s">
-        <v>269</v>
-      </c>
-      <c r="R17" s="178"/>
-      <c r="S17" s="178"/>
-      <c r="T17" s="178"/>
-      <c r="U17" s="178"/>
-      <c r="V17" s="179"/>
-      <c r="AL17" s="62"/>
+      <c r="E17" s="58"/>
+      <c r="H17" s="174" t="s">
+        <v>230</v>
+      </c>
+      <c r="I17" s="175"/>
+      <c r="J17" s="175"/>
+      <c r="K17" s="175"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="175"/>
+      <c r="N17" s="176"/>
+      <c r="Q17" s="174" t="s">
+        <v>231</v>
+      </c>
+      <c r="R17" s="175"/>
+      <c r="S17" s="175"/>
+      <c r="T17" s="175"/>
+      <c r="U17" s="175"/>
+      <c r="V17" s="176"/>
+      <c r="AL17" s="59"/>
     </row>
     <row r="18" spans="5:71" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E18" s="61"/>
-      <c r="H18" s="180"/>
-      <c r="I18" s="181"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="181"/>
-      <c r="L18" s="181"/>
-      <c r="M18" s="181"/>
-      <c r="N18" s="182"/>
-      <c r="Q18" s="180"/>
-      <c r="R18" s="181"/>
-      <c r="S18" s="181"/>
-      <c r="T18" s="181"/>
-      <c r="U18" s="181"/>
-      <c r="V18" s="182"/>
-      <c r="AL18" s="62"/>
-      <c r="BO18" s="152" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP18" s="153"/>
-      <c r="BQ18" s="153"/>
-      <c r="BR18" s="205"/>
-      <c r="BS18" s="38"/>
+      <c r="E18" s="58"/>
+      <c r="H18" s="177"/>
+      <c r="I18" s="178"/>
+      <c r="J18" s="178"/>
+      <c r="K18" s="178"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="178"/>
+      <c r="N18" s="179"/>
+      <c r="Q18" s="177"/>
+      <c r="R18" s="178"/>
+      <c r="S18" s="178"/>
+      <c r="T18" s="178"/>
+      <c r="U18" s="178"/>
+      <c r="V18" s="179"/>
+      <c r="AL18" s="59"/>
+      <c r="BO18" s="132" t="s">
+        <v>226</v>
+      </c>
+      <c r="BP18" s="133"/>
+      <c r="BQ18" s="133"/>
+      <c r="BR18" s="160"/>
+      <c r="BS18" s="35"/>
     </row>
     <row r="19" spans="5:71" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="E19" s="61"/>
-      <c r="H19" s="183" t="str">
+      <c r="E19" s="58"/>
+      <c r="H19" s="180" t="str">
         <f>INDEX(BP40:BP42,MATCH(MAX(BT40:BT42),BT40:BT42,0))</f>
         <v>Vendor B</v>
       </c>
-      <c r="I19" s="184"/>
-      <c r="J19" s="184"/>
-      <c r="K19" s="184"/>
-      <c r="L19" s="184"/>
-      <c r="M19" s="184"/>
-      <c r="N19" s="185"/>
-      <c r="Q19" s="195" t="str">
+      <c r="I19" s="181"/>
+      <c r="J19" s="181"/>
+      <c r="K19" s="181"/>
+      <c r="L19" s="181"/>
+      <c r="M19" s="181"/>
+      <c r="N19" s="182"/>
+      <c r="Q19" s="192" t="str">
         <f>BP30</f>
         <v>K-1-PUTIH</v>
       </c>
-      <c r="R19" s="196"/>
-      <c r="S19" s="192" t="str">
+      <c r="R19" s="193"/>
+      <c r="S19" s="189" t="str">
         <f>BP31</f>
         <v>K-1-HITAM</v>
       </c>
-      <c r="T19" s="194"/>
-      <c r="U19" s="192" t="str">
+      <c r="T19" s="191"/>
+      <c r="U19" s="189" t="str">
         <f>BP32</f>
         <v>K-1-ABU-ABU</v>
       </c>
-      <c r="V19" s="193"/>
-      <c r="AL19" s="62"/>
-      <c r="BO19" s="84" t="s">
+      <c r="V19" s="190"/>
+      <c r="AL19" s="59"/>
+      <c r="BO19" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BP19" s="84"/>
+      <c r="BP19" s="70"/>
       <c r="BQ19" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="BR19" s="52" t="s">
-        <v>97</v>
+        <v>68</v>
+      </c>
+      <c r="BR19" s="49" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E20" s="61"/>
-      <c r="H20" s="186"/>
-      <c r="I20" s="187"/>
-      <c r="J20" s="187"/>
-      <c r="K20" s="187"/>
-      <c r="L20" s="187"/>
-      <c r="M20" s="187"/>
-      <c r="N20" s="188"/>
-      <c r="Q20" s="201">
+      <c r="E20" s="58"/>
+      <c r="H20" s="183"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="184"/>
+      <c r="K20" s="184"/>
+      <c r="L20" s="184"/>
+      <c r="M20" s="184"/>
+      <c r="N20" s="185"/>
+      <c r="Q20" s="154">
         <f>BQ30</f>
         <v>57</v>
       </c>
-      <c r="R20" s="197"/>
-      <c r="S20" s="197">
+      <c r="R20" s="155"/>
+      <c r="S20" s="155">
         <f>BQ31</f>
         <v>90</v>
       </c>
-      <c r="T20" s="197"/>
-      <c r="U20" s="197">
+      <c r="T20" s="155"/>
+      <c r="U20" s="155">
         <f>BQ32</f>
         <v>98</v>
       </c>
-      <c r="V20" s="198"/>
-      <c r="AL20" s="62"/>
-      <c r="BO20" s="176" t="s">
+      <c r="V20" s="194"/>
+      <c r="AL20" s="59"/>
+      <c r="BO20" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="BP20" s="176"/>
+      <c r="BP20" s="173"/>
       <c r="BQ20" s="22">
         <f>'ADMINISTRASI DEFECT'!N7</f>
         <v>2</v>
@@ -11248,25 +10602,25 @@
       </c>
     </row>
     <row r="21" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E21" s="61"/>
-      <c r="H21" s="186"/>
-      <c r="I21" s="187"/>
-      <c r="J21" s="187"/>
-      <c r="K21" s="187"/>
-      <c r="L21" s="187"/>
-      <c r="M21" s="187"/>
-      <c r="N21" s="188"/>
-      <c r="Q21" s="201"/>
-      <c r="R21" s="197"/>
-      <c r="S21" s="197"/>
-      <c r="T21" s="197"/>
-      <c r="U21" s="197"/>
-      <c r="V21" s="198"/>
-      <c r="AL21" s="62"/>
-      <c r="BO21" s="176" t="s">
+      <c r="E21" s="58"/>
+      <c r="H21" s="183"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="184"/>
+      <c r="L21" s="184"/>
+      <c r="M21" s="184"/>
+      <c r="N21" s="185"/>
+      <c r="Q21" s="154"/>
+      <c r="R21" s="155"/>
+      <c r="S21" s="155"/>
+      <c r="T21" s="155"/>
+      <c r="U21" s="155"/>
+      <c r="V21" s="194"/>
+      <c r="AL21" s="59"/>
+      <c r="BO21" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="BP21" s="176"/>
+      <c r="BP21" s="173"/>
       <c r="BQ21" s="22">
         <f>'ADMINISTRASI DEFECT'!N8</f>
         <v>1</v>
@@ -11277,26 +10631,26 @@
       </c>
     </row>
     <row r="22" spans="5:71" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E22" s="61"/>
-      <c r="H22" s="189"/>
-      <c r="I22" s="190"/>
-      <c r="J22" s="190"/>
-      <c r="K22" s="190"/>
-      <c r="L22" s="190"/>
-      <c r="M22" s="190"/>
-      <c r="N22" s="191"/>
-      <c r="Q22" s="202"/>
-      <c r="R22" s="199"/>
-      <c r="S22" s="199"/>
-      <c r="T22" s="199"/>
-      <c r="U22" s="199"/>
-      <c r="V22" s="200"/>
-      <c r="AL22" s="62"/>
-      <c r="BO22" s="176" t="s">
+      <c r="E22" s="58"/>
+      <c r="H22" s="186"/>
+      <c r="I22" s="187"/>
+      <c r="J22" s="187"/>
+      <c r="K22" s="187"/>
+      <c r="L22" s="187"/>
+      <c r="M22" s="187"/>
+      <c r="N22" s="188"/>
+      <c r="Q22" s="156"/>
+      <c r="R22" s="157"/>
+      <c r="S22" s="157"/>
+      <c r="T22" s="157"/>
+      <c r="U22" s="157"/>
+      <c r="V22" s="195"/>
+      <c r="AL22" s="59"/>
+      <c r="BO22" s="173" t="s">
         <v>13</v>
       </c>
-      <c r="BP22" s="176"/>
-      <c r="BQ22" s="53">
+      <c r="BP22" s="173"/>
+      <c r="BQ22" s="50">
         <f>'ADMINISTRASI DEFECT'!N9</f>
         <v>0</v>
       </c>
@@ -11306,50 +10660,50 @@
       </c>
     </row>
     <row r="23" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E23" s="61"/>
-      <c r="AL23" s="62"/>
+      <c r="E23" s="58"/>
+      <c r="AL23" s="59"/>
     </row>
     <row r="24" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E24" s="61"/>
-      <c r="AL24" s="62"/>
+      <c r="E24" s="58"/>
+      <c r="AL24" s="59"/>
     </row>
     <row r="25" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E25" s="61"/>
-      <c r="AL25" s="62"/>
+      <c r="E25" s="58"/>
+      <c r="AL25" s="59"/>
     </row>
     <row r="26" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E26" s="61"/>
-      <c r="AL26" s="62"/>
+      <c r="E26" s="58"/>
+      <c r="AL26" s="59"/>
     </row>
     <row r="27" spans="5:71" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E27" s="61"/>
-      <c r="AL27" s="62"/>
+      <c r="E27" s="58"/>
+      <c r="AL27" s="59"/>
     </row>
     <row r="28" spans="5:71" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E28" s="61"/>
-      <c r="AL28" s="62"/>
-      <c r="BP28" s="203" t="s">
-        <v>265</v>
-      </c>
-      <c r="BQ28" s="204"/>
-      <c r="BR28" s="205"/>
+      <c r="E28" s="58"/>
+      <c r="AL28" s="59"/>
+      <c r="BP28" s="158" t="s">
+        <v>227</v>
+      </c>
+      <c r="BQ28" s="159"/>
+      <c r="BR28" s="160"/>
     </row>
     <row r="29" spans="5:71" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="E29" s="61"/>
-      <c r="AL29" s="62"/>
-      <c r="BP29" s="52" t="s">
+      <c r="E29" s="58"/>
+      <c r="AL29" s="59"/>
+      <c r="BP29" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="BQ29" s="52" t="s">
+      <c r="BQ29" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="BR29" s="52" t="s">
+      <c r="BR29" s="49" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E30" s="61"/>
-      <c r="AL30" s="62"/>
+      <c r="E30" s="58"/>
+      <c r="AL30" s="59"/>
       <c r="BP30" s="22" t="str">
         <f>'IMPLEMENTASI FIFO'!K8</f>
         <v>K-1-PUTIH</v>
@@ -11364,8 +10718,8 @@
       </c>
     </row>
     <row r="31" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E31" s="61"/>
-      <c r="AL31" s="62"/>
+      <c r="E31" s="58"/>
+      <c r="AL31" s="59"/>
       <c r="BP31" s="22" t="str">
         <f>'IMPLEMENTASI FIFO'!K9</f>
         <v>K-1-HITAM</v>
@@ -11380,8 +10734,8 @@
       </c>
     </row>
     <row r="32" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E32" s="61"/>
-      <c r="AL32" s="62"/>
+      <c r="E32" s="58"/>
+      <c r="AL32" s="59"/>
       <c r="BP32" s="22" t="str">
         <f>'IMPLEMENTASI FIFO'!K10</f>
         <v>K-1-ABU-ABU</v>
@@ -11396,79 +10750,79 @@
       </c>
     </row>
     <row r="33" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E33" s="61"/>
-      <c r="AL33" s="62"/>
+      <c r="E33" s="58"/>
+      <c r="AL33" s="59"/>
     </row>
     <row r="34" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E34" s="61"/>
-      <c r="AL34" s="62"/>
+      <c r="E34" s="58"/>
+      <c r="AL34" s="59"/>
     </row>
     <row r="35" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E35" s="61"/>
-      <c r="AL35" s="62"/>
+      <c r="E35" s="58"/>
+      <c r="AL35" s="59"/>
     </row>
     <row r="36" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E36" s="61"/>
-      <c r="AL36" s="62"/>
+      <c r="E36" s="58"/>
+      <c r="AL36" s="59"/>
     </row>
     <row r="37" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E37" s="61"/>
-      <c r="AL37" s="62"/>
+      <c r="E37" s="58"/>
+      <c r="AL37" s="59"/>
     </row>
     <row r="38" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E38" s="61"/>
-      <c r="AL38" s="62"/>
-      <c r="BP38" s="203" t="s">
-        <v>263</v>
-      </c>
-      <c r="BQ38" s="204"/>
-      <c r="BR38" s="204"/>
-      <c r="BS38" s="204"/>
-      <c r="BT38" s="204"/>
-      <c r="BU38" s="205"/>
+      <c r="E38" s="58"/>
+      <c r="AL38" s="59"/>
+      <c r="BP38" s="158" t="s">
+        <v>225</v>
+      </c>
+      <c r="BQ38" s="159"/>
+      <c r="BR38" s="159"/>
+      <c r="BS38" s="159"/>
+      <c r="BT38" s="159"/>
+      <c r="BU38" s="160"/>
     </row>
     <row r="39" spans="5:73" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="E39" s="61"/>
-      <c r="AL39" s="62"/>
-      <c r="BP39" s="52" t="s">
+      <c r="E39" s="58"/>
+      <c r="AL39" s="59"/>
+      <c r="BP39" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="BQ39" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="BR39" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="BS39" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="BT39" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="BU39" s="52" t="s">
-        <v>94</v>
+      <c r="BQ39" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="BR39" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="BS39" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="BT39" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="BU39" s="49" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E40" s="61"/>
-      <c r="AL40" s="62"/>
+      <c r="E40" s="58"/>
+      <c r="AL40" s="59"/>
       <c r="BP40" s="22" t="str">
         <f>'IMPLEMENTASI VPI'!D23</f>
         <v>Vendor A</v>
       </c>
-      <c r="BQ40" s="29">
+      <c r="BQ40" s="26">
         <f>'IMPLEMENTASI VPI'!E23</f>
         <v>50</v>
       </c>
-      <c r="BR40" s="29">
+      <c r="BR40" s="26">
         <f>'IMPLEMENTASI VPI'!F23</f>
         <v>100</v>
       </c>
-      <c r="BS40" s="29">
+      <c r="BS40" s="26">
         <f>'IMPLEMENTASI VPI'!G23</f>
         <v>96</v>
       </c>
-      <c r="BT40" s="29">
+      <c r="BT40" s="26">
         <f>'IMPLEMENTASI VPI'!H23</f>
         <v>74.2</v>
       </c>
@@ -11478,25 +10832,25 @@
       </c>
     </row>
     <row r="41" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E41" s="61"/>
-      <c r="AL41" s="62"/>
+      <c r="E41" s="58"/>
+      <c r="AL41" s="59"/>
       <c r="BP41" s="22" t="str">
         <f>'IMPLEMENTASI VPI'!D24</f>
         <v>Vendor B</v>
       </c>
-      <c r="BQ41" s="29">
+      <c r="BQ41" s="26">
         <f>'IMPLEMENTASI VPI'!E24</f>
         <v>100</v>
       </c>
-      <c r="BR41" s="29">
+      <c r="BR41" s="26">
         <f>'IMPLEMENTASI VPI'!F24</f>
         <v>100</v>
       </c>
-      <c r="BS41" s="29">
+      <c r="BS41" s="26">
         <f>'IMPLEMENTASI VPI'!G24</f>
         <v>98.630136986301366</v>
       </c>
-      <c r="BT41" s="29">
+      <c r="BT41" s="26">
         <f>'IMPLEMENTASI VPI'!H24</f>
         <v>99.726027397260282</v>
       </c>
@@ -11506,25 +10860,25 @@
       </c>
     </row>
     <row r="42" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E42" s="61"/>
-      <c r="AL42" s="62"/>
+      <c r="E42" s="58"/>
+      <c r="AL42" s="59"/>
       <c r="BP42" s="22" t="str">
         <f>'IMPLEMENTASI VPI'!D25</f>
         <v>Vendor C</v>
       </c>
-      <c r="BQ42" s="29">
+      <c r="BQ42" s="26">
         <f>'IMPLEMENTASI VPI'!E25</f>
         <v>0</v>
       </c>
-      <c r="BR42" s="29">
+      <c r="BR42" s="26">
         <f>'IMPLEMENTASI VPI'!F25</f>
         <v>0</v>
       </c>
-      <c r="BS42" s="29">
+      <c r="BS42" s="26">
         <f>'IMPLEMENTASI VPI'!G25</f>
         <v>100</v>
       </c>
-      <c r="BT42" s="29">
+      <c r="BT42" s="26">
         <f>'IMPLEMENTASI VPI'!H25</f>
         <v>20</v>
       </c>
@@ -11534,430 +10888,432 @@
       </c>
     </row>
     <row r="43" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E43" s="61"/>
-      <c r="AL43" s="62"/>
+      <c r="E43" s="58"/>
+      <c r="AL43" s="59"/>
     </row>
     <row r="44" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E44" s="61"/>
-      <c r="AL44" s="62"/>
+      <c r="E44" s="58"/>
+      <c r="AL44" s="59"/>
     </row>
     <row r="45" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E45" s="61"/>
-      <c r="AL45" s="62"/>
+      <c r="E45" s="58"/>
+      <c r="AL45" s="59"/>
     </row>
     <row r="46" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E46" s="61"/>
-      <c r="AL46" s="62"/>
+      <c r="E46" s="58"/>
+      <c r="AL46" s="59"/>
     </row>
     <row r="47" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E47" s="61"/>
-      <c r="AL47" s="62"/>
+      <c r="E47" s="58"/>
+      <c r="AL47" s="59"/>
     </row>
     <row r="48" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E48" s="61"/>
-      <c r="AL48" s="62"/>
-      <c r="BP48" s="173" t="s">
-        <v>267</v>
-      </c>
-      <c r="BQ48" s="174"/>
-      <c r="BR48" s="174"/>
-      <c r="BS48" s="175"/>
-      <c r="BT48" s="55"/>
+      <c r="E48" s="58"/>
+      <c r="AL48" s="59"/>
+      <c r="BP48" s="170" t="s">
+        <v>229</v>
+      </c>
+      <c r="BQ48" s="171"/>
+      <c r="BR48" s="171"/>
+      <c r="BS48" s="172"/>
+      <c r="BT48" s="52"/>
     </row>
     <row r="49" spans="5:71" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="E49" s="61"/>
-      <c r="AL49" s="62"/>
-      <c r="BP49" s="56" t="s">
+      <c r="E49" s="58"/>
+      <c r="AL49" s="59"/>
+      <c r="BP49" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="BQ49" s="56" t="s">
-        <v>266</v>
-      </c>
-      <c r="BR49" s="56" t="s">
-        <v>261</v>
-      </c>
-      <c r="BS49" s="56" t="s">
-        <v>262</v>
+      <c r="BQ49" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="BR49" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="BS49" s="53" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E50" s="61"/>
-      <c r="AL50" s="62"/>
-      <c r="BP50" s="57" t="str">
+      <c r="E50" s="58"/>
+      <c r="AL50" s="59"/>
+      <c r="BP50" s="54" t="str">
         <f>'ADMINISTRASI DEFECT'!B7</f>
         <v>Vendor A</v>
       </c>
-      <c r="BQ50" s="57">
+      <c r="BQ50" s="54">
         <f>'ADMINISTRASI DEFECT'!D7</f>
         <v>2</v>
       </c>
-      <c r="BR50" s="57">
+      <c r="BR50" s="54">
         <f>'ADMINISTRASI DEFECT'!G7</f>
         <v>1</v>
       </c>
-      <c r="BS50" s="57">
+      <c r="BS50" s="54">
         <f>'ADMINISTRASI DEFECT'!H7</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E51" s="61"/>
-      <c r="AL51" s="62"/>
-      <c r="BP51" s="57" t="str">
+      <c r="E51" s="58"/>
+      <c r="AL51" s="59"/>
+      <c r="BP51" s="54" t="str">
         <f>'ADMINISTRASI DEFECT'!B8</f>
         <v>Vendor B</v>
       </c>
-      <c r="BQ51" s="57">
+      <c r="BQ51" s="54">
         <f>'ADMINISTRASI DEFECT'!D8</f>
         <v>2</v>
       </c>
-      <c r="BR51" s="57">
+      <c r="BR51" s="54">
         <f>'ADMINISTRASI DEFECT'!G8</f>
         <v>2</v>
       </c>
-      <c r="BS51" s="57">
+      <c r="BS51" s="54">
         <f>'ADMINISTRASI DEFECT'!H8</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E52" s="61"/>
-      <c r="AL52" s="62"/>
-      <c r="BP52" s="57" t="str">
+      <c r="E52" s="58"/>
+      <c r="AL52" s="59"/>
+      <c r="BP52" s="54" t="str">
         <f>'ADMINISTRASI DEFECT'!B9</f>
         <v>Vendor C</v>
       </c>
-      <c r="BQ52" s="57">
+      <c r="BQ52" s="54">
         <f>'ADMINISTRASI DEFECT'!D9</f>
         <v>2</v>
       </c>
-      <c r="BR52" s="57">
+      <c r="BR52" s="54">
         <f>'ADMINISTRASI DEFECT'!G9</f>
         <v>0</v>
       </c>
-      <c r="BS52" s="57">
+      <c r="BS52" s="54">
         <f>'ADMINISTRASI DEFECT'!H9</f>
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E53" s="61"/>
-      <c r="AL53" s="62"/>
+      <c r="E53" s="58"/>
+      <c r="AL53" s="59"/>
     </row>
     <row r="54" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E54" s="61"/>
-      <c r="AL54" s="62"/>
+      <c r="E54" s="58"/>
+      <c r="AL54" s="59"/>
     </row>
     <row r="55" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E55" s="61"/>
-      <c r="AL55" s="62"/>
+      <c r="E55" s="58"/>
+      <c r="AL55" s="59"/>
     </row>
     <row r="56" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E56" s="61"/>
-      <c r="AL56" s="62"/>
+      <c r="E56" s="58"/>
+      <c r="AL56" s="59"/>
     </row>
     <row r="57" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E57" s="61"/>
-      <c r="AL57" s="62"/>
+      <c r="E57" s="58"/>
+      <c r="AL57" s="59"/>
     </row>
     <row r="58" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E58" s="61"/>
-      <c r="AL58" s="62"/>
+      <c r="E58" s="58"/>
+      <c r="AL58" s="59"/>
     </row>
     <row r="59" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E59" s="61"/>
-      <c r="AL59" s="62"/>
+      <c r="E59" s="58"/>
+      <c r="AL59" s="59"/>
     </row>
     <row r="60" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E60" s="61"/>
-      <c r="AL60" s="62"/>
+      <c r="E60" s="58"/>
+      <c r="AL60" s="59"/>
     </row>
     <row r="61" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E61" s="61"/>
-      <c r="AL61" s="62"/>
+      <c r="E61" s="58"/>
+      <c r="AL61" s="59"/>
     </row>
     <row r="62" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E62" s="61"/>
-      <c r="AL62" s="62"/>
+      <c r="E62" s="58"/>
+      <c r="AL62" s="59"/>
     </row>
     <row r="63" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E63" s="61"/>
-      <c r="AL63" s="62"/>
+      <c r="E63" s="58"/>
+      <c r="AL63" s="59"/>
     </row>
     <row r="64" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E64" s="61"/>
-      <c r="AL64" s="62"/>
+      <c r="E64" s="58"/>
+      <c r="AL64" s="59"/>
     </row>
     <row r="65" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E65" s="61"/>
-      <c r="AL65" s="62"/>
+      <c r="E65" s="58"/>
+      <c r="AL65" s="59"/>
     </row>
     <row r="66" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E66" s="61"/>
-      <c r="AL66" s="62"/>
+      <c r="E66" s="58"/>
+      <c r="AL66" s="59"/>
     </row>
     <row r="67" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E67" s="61"/>
-      <c r="AL67" s="62"/>
+      <c r="E67" s="58"/>
+      <c r="AL67" s="59"/>
     </row>
     <row r="68" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E68" s="61"/>
-      <c r="AL68" s="62"/>
+      <c r="E68" s="58"/>
+      <c r="AL68" s="59"/>
     </row>
     <row r="69" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E69" s="61"/>
-      <c r="AL69" s="62"/>
+      <c r="E69" s="58"/>
+      <c r="AL69" s="59"/>
     </row>
     <row r="70" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E70" s="61"/>
-      <c r="AL70" s="62"/>
+      <c r="E70" s="58"/>
+      <c r="AL70" s="59"/>
     </row>
     <row r="71" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E71" s="61"/>
-      <c r="AL71" s="62"/>
+      <c r="E71" s="58"/>
+      <c r="AL71" s="59"/>
     </row>
     <row r="72" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E72" s="61"/>
-      <c r="AL72" s="62"/>
+      <c r="E72" s="58"/>
+      <c r="AL72" s="59"/>
     </row>
     <row r="73" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E73" s="61"/>
-      <c r="AL73" s="62"/>
+      <c r="E73" s="58"/>
+      <c r="AL73" s="59"/>
     </row>
     <row r="74" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E74" s="61"/>
-      <c r="AL74" s="62"/>
+      <c r="E74" s="58"/>
+      <c r="AL74" s="59"/>
     </row>
     <row r="75" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E75" s="61"/>
-      <c r="AL75" s="62"/>
+      <c r="E75" s="58"/>
+      <c r="AL75" s="59"/>
     </row>
     <row r="76" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E76" s="61"/>
-      <c r="AL76" s="62"/>
+      <c r="E76" s="58"/>
+      <c r="AL76" s="59"/>
     </row>
     <row r="77" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E77" s="61"/>
-      <c r="AL77" s="62"/>
+      <c r="E77" s="58"/>
+      <c r="AL77" s="59"/>
     </row>
     <row r="78" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E78" s="61"/>
-      <c r="AL78" s="62"/>
+      <c r="E78" s="58"/>
+      <c r="AL78" s="59"/>
     </row>
     <row r="79" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E79" s="61"/>
-      <c r="AL79" s="62"/>
+      <c r="E79" s="58"/>
+      <c r="AL79" s="59"/>
     </row>
     <row r="80" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E80" s="61"/>
-      <c r="AL80" s="62"/>
+      <c r="E80" s="58"/>
+      <c r="AL80" s="59"/>
     </row>
     <row r="81" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E81" s="61"/>
-      <c r="AL81" s="62"/>
+      <c r="E81" s="58"/>
+      <c r="AL81" s="59"/>
     </row>
     <row r="82" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E82" s="61"/>
-      <c r="AL82" s="62"/>
+      <c r="E82" s="58"/>
+      <c r="AL82" s="59"/>
     </row>
     <row r="83" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E83" s="61"/>
-      <c r="AL83" s="62"/>
+      <c r="E83" s="58"/>
+      <c r="AL83" s="59"/>
     </row>
     <row r="84" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E84" s="61"/>
-      <c r="AL84" s="62"/>
+      <c r="E84" s="58"/>
+      <c r="AL84" s="59"/>
     </row>
     <row r="85" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E85" s="61"/>
-      <c r="AL85" s="62"/>
+      <c r="E85" s="58"/>
+      <c r="AL85" s="59"/>
     </row>
     <row r="86" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E86" s="61"/>
-      <c r="AL86" s="62"/>
+      <c r="E86" s="58"/>
+      <c r="AL86" s="59"/>
     </row>
     <row r="87" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E87" s="61"/>
-      <c r="AL87" s="62"/>
+      <c r="E87" s="58"/>
+      <c r="AL87" s="59"/>
     </row>
     <row r="88" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E88" s="61"/>
-      <c r="AL88" s="62"/>
+      <c r="E88" s="58"/>
+      <c r="AL88" s="59"/>
     </row>
     <row r="89" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E89" s="61"/>
-      <c r="AL89" s="62"/>
+      <c r="E89" s="58"/>
+      <c r="AL89" s="59"/>
     </row>
     <row r="90" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E90" s="61"/>
-      <c r="AL90" s="62"/>
+      <c r="E90" s="58"/>
+      <c r="AL90" s="59"/>
     </row>
     <row r="91" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E91" s="61"/>
-      <c r="AL91" s="62"/>
+      <c r="E91" s="58"/>
+      <c r="AL91" s="59"/>
     </row>
     <row r="92" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E92" s="61"/>
-      <c r="AL92" s="62"/>
+      <c r="E92" s="58"/>
+      <c r="AL92" s="59"/>
     </row>
     <row r="93" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E93" s="61"/>
-      <c r="AL93" s="62"/>
+      <c r="E93" s="58"/>
+      <c r="AL93" s="59"/>
     </row>
     <row r="94" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E94" s="61"/>
-      <c r="AL94" s="62"/>
+      <c r="E94" s="58"/>
+      <c r="AL94" s="59"/>
     </row>
     <row r="95" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E95" s="61"/>
-      <c r="AL95" s="62"/>
+      <c r="E95" s="58"/>
+      <c r="AL95" s="59"/>
     </row>
     <row r="96" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E96" s="61"/>
-      <c r="AL96" s="62"/>
+      <c r="E96" s="58"/>
+      <c r="AL96" s="59"/>
     </row>
     <row r="97" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E97" s="61"/>
-      <c r="AL97" s="62"/>
+      <c r="E97" s="58"/>
+      <c r="AL97" s="59"/>
     </row>
     <row r="98" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E98" s="61"/>
-      <c r="AL98" s="62"/>
+      <c r="E98" s="58"/>
+      <c r="AL98" s="59"/>
     </row>
     <row r="99" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E99" s="61"/>
-      <c r="AL99" s="62"/>
+      <c r="E99" s="58"/>
+      <c r="AL99" s="59"/>
     </row>
     <row r="100" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E100" s="61"/>
-      <c r="AL100" s="62"/>
+      <c r="E100" s="58"/>
+      <c r="AL100" s="59"/>
     </row>
     <row r="101" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E101" s="61"/>
-      <c r="AL101" s="62"/>
+      <c r="E101" s="58"/>
+      <c r="AL101" s="59"/>
     </row>
     <row r="102" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E102" s="61"/>
-      <c r="AL102" s="62"/>
+      <c r="E102" s="58"/>
+      <c r="AL102" s="59"/>
     </row>
     <row r="103" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E103" s="61"/>
-      <c r="AL103" s="62"/>
+      <c r="E103" s="58"/>
+      <c r="AL103" s="59"/>
     </row>
     <row r="104" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E104" s="61"/>
-      <c r="AL104" s="62"/>
+      <c r="E104" s="58"/>
+      <c r="AL104" s="59"/>
     </row>
     <row r="105" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E105" s="61"/>
-      <c r="AL105" s="62"/>
+      <c r="E105" s="58"/>
+      <c r="AL105" s="59"/>
     </row>
     <row r="106" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E106" s="61"/>
-      <c r="AL106" s="62"/>
+      <c r="E106" s="58"/>
+      <c r="AL106" s="59"/>
     </row>
     <row r="107" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E107" s="61"/>
-      <c r="AL107" s="62"/>
+      <c r="E107" s="58"/>
+      <c r="AL107" s="59"/>
     </row>
     <row r="108" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E108" s="61"/>
-      <c r="AL108" s="62"/>
+      <c r="E108" s="58"/>
+      <c r="AL108" s="59"/>
     </row>
     <row r="109" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E109" s="61"/>
-      <c r="AL109" s="62"/>
+      <c r="E109" s="58"/>
+      <c r="AL109" s="59"/>
     </row>
     <row r="110" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E110" s="61"/>
-      <c r="AL110" s="62"/>
+      <c r="E110" s="58"/>
+      <c r="AL110" s="59"/>
     </row>
     <row r="111" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E111" s="61"/>
-      <c r="AL111" s="62"/>
+      <c r="E111" s="58"/>
+      <c r="AL111" s="59"/>
     </row>
     <row r="112" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E112" s="61"/>
-      <c r="AL112" s="62"/>
+      <c r="E112" s="58"/>
+      <c r="AL112" s="59"/>
     </row>
     <row r="113" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E113" s="61"/>
-      <c r="AL113" s="62"/>
+      <c r="E113" s="58"/>
+      <c r="AL113" s="59"/>
     </row>
     <row r="114" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E114" s="61"/>
-      <c r="AL114" s="62"/>
+      <c r="E114" s="58"/>
+      <c r="AL114" s="59"/>
     </row>
     <row r="115" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E115" s="61"/>
-      <c r="AL115" s="62"/>
+      <c r="E115" s="58"/>
+      <c r="AL115" s="59"/>
     </row>
     <row r="116" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E116" s="61"/>
-      <c r="AL116" s="62"/>
+      <c r="E116" s="58"/>
+      <c r="AL116" s="59"/>
     </row>
     <row r="117" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E117" s="61"/>
-      <c r="AL117" s="62"/>
+      <c r="E117" s="58"/>
+      <c r="AL117" s="59"/>
     </row>
     <row r="118" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E118" s="61"/>
-      <c r="AL118" s="62"/>
+      <c r="E118" s="58"/>
+      <c r="AL118" s="59"/>
     </row>
     <row r="119" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E119" s="61"/>
-      <c r="AL119" s="62"/>
+      <c r="E119" s="58"/>
+      <c r="AL119" s="59"/>
     </row>
     <row r="120" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E120" s="61"/>
-      <c r="AL120" s="62"/>
+      <c r="E120" s="58"/>
+      <c r="AL120" s="59"/>
     </row>
     <row r="121" spans="5:38" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E121" s="63"/>
-      <c r="F121" s="64"/>
-      <c r="G121" s="64"/>
-      <c r="H121" s="64"/>
-      <c r="I121" s="64"/>
-      <c r="J121" s="64"/>
-      <c r="K121" s="64"/>
-      <c r="L121" s="64"/>
-      <c r="M121" s="64"/>
-      <c r="N121" s="64"/>
-      <c r="O121" s="64"/>
-      <c r="P121" s="64"/>
-      <c r="Q121" s="64"/>
-      <c r="R121" s="64"/>
-      <c r="S121" s="64"/>
-      <c r="T121" s="64"/>
-      <c r="U121" s="64"/>
-      <c r="V121" s="64"/>
-      <c r="W121" s="64"/>
-      <c r="X121" s="64"/>
-      <c r="Y121" s="64"/>
-      <c r="Z121" s="64"/>
-      <c r="AA121" s="64"/>
-      <c r="AB121" s="64"/>
-      <c r="AC121" s="64"/>
-      <c r="AD121" s="64"/>
-      <c r="AE121" s="64"/>
-      <c r="AF121" s="64"/>
-      <c r="AG121" s="64"/>
-      <c r="AH121" s="64"/>
-      <c r="AI121" s="64"/>
-      <c r="AJ121" s="64"/>
-      <c r="AK121" s="64"/>
-      <c r="AL121" s="65"/>
+      <c r="E121" s="60"/>
+      <c r="F121" s="61"/>
+      <c r="G121" s="61"/>
+      <c r="H121" s="61"/>
+      <c r="I121" s="61"/>
+      <c r="J121" s="61"/>
+      <c r="K121" s="61"/>
+      <c r="L121" s="61"/>
+      <c r="M121" s="61"/>
+      <c r="N121" s="61"/>
+      <c r="O121" s="61"/>
+      <c r="P121" s="61"/>
+      <c r="Q121" s="61"/>
+      <c r="R121" s="61"/>
+      <c r="S121" s="61"/>
+      <c r="T121" s="61"/>
+      <c r="U121" s="61"/>
+      <c r="V121" s="61"/>
+      <c r="W121" s="61"/>
+      <c r="X121" s="61"/>
+      <c r="Y121" s="61"/>
+      <c r="Z121" s="61"/>
+      <c r="AA121" s="61"/>
+      <c r="AB121" s="61"/>
+      <c r="AC121" s="61"/>
+      <c r="AD121" s="61"/>
+      <c r="AE121" s="61"/>
+      <c r="AF121" s="61"/>
+      <c r="AG121" s="61"/>
+      <c r="AH121" s="61"/>
+      <c r="AI121" s="61"/>
+      <c r="AJ121" s="61"/>
+      <c r="AK121" s="61"/>
+      <c r="AL121" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="BP38:BU38"/>
-    <mergeCell ref="BO18:BR18"/>
-    <mergeCell ref="K5:AD9"/>
     <mergeCell ref="BP48:BS48"/>
     <mergeCell ref="BO19:BP19"/>
     <mergeCell ref="BO22:BP22"/>
     <mergeCell ref="BO21:BP21"/>
     <mergeCell ref="BO20:BP20"/>
+    <mergeCell ref="Q20:R22"/>
+    <mergeCell ref="BP28:BR28"/>
+    <mergeCell ref="BP38:BU38"/>
+    <mergeCell ref="BO18:BR18"/>
+    <mergeCell ref="K5:AD9"/>
     <mergeCell ref="Q17:V18"/>
     <mergeCell ref="H19:N22"/>
     <mergeCell ref="H17:N18"/>
@@ -11966,8 +11322,6 @@
     <mergeCell ref="Q19:R19"/>
     <mergeCell ref="U20:V22"/>
     <mergeCell ref="S20:T22"/>
-    <mergeCell ref="Q20:R22"/>
-    <mergeCell ref="BP28:BR28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Simulasi Manual TA Rionaldo Fransiskus Silaen.xlsx
+++ b/data/Simulasi Manual TA Rionaldo Fransiskus Silaen.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rionaldosilaen\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39000432-60D4-4267-8690-491474241FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95083303-F3E6-42CE-B786-62D21C1726F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="632" xr2:uid="{51C07C40-CE71-4EF6-8E1B-C1439EB1384E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="632" firstSheet="1" activeTab="2" xr2:uid="{51C07C40-CE71-4EF6-8E1B-C1439EB1384E}"/>
   </bookViews>
   <sheets>
-    <sheet name="IMPLEMENTASI PEMESANAN BARANG" sheetId="7" r:id="rId1"/>
-    <sheet name="IMPLEMENTASI QUALITY CONTROL" sheetId="2" r:id="rId2"/>
-    <sheet name="IMPLEMENTASI FIFO" sheetId="1" r:id="rId3"/>
-    <sheet name="ADMINISTRASI DEFECT" sheetId="3" r:id="rId4"/>
-    <sheet name="IMPLEMENTASI VPI" sheetId="5" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="9" r:id="rId6"/>
+    <sheet name="IMPLEMENTASI MRP" sheetId="4" r:id="rId1"/>
+    <sheet name="IMPLEMENTASI PEMESANAN BARANG" sheetId="7" r:id="rId2"/>
+    <sheet name="IMPLEMENTASI QUALITY CONTROL" sheetId="2" r:id="rId3"/>
+    <sheet name="IMPLEMENTASI FIFO" sheetId="1" r:id="rId4"/>
+    <sheet name="ADMINISTRASI DEFECT" sheetId="3" r:id="rId5"/>
+    <sheet name="IMPLEMENTASI VPI" sheetId="5" r:id="rId6"/>
+    <sheet name="Dasbord" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="271">
   <si>
     <t>Tanggal</t>
   </si>
@@ -222,9 +223,105 @@
     <t>Total Hasil Akhir Return</t>
   </si>
   <si>
+    <t>MASTER PRODUCTION SCHEDULE (MPS)</t>
+  </si>
+  <si>
+    <t>Minggu 1</t>
+  </si>
+  <si>
+    <t>Minggu 2</t>
+  </si>
+  <si>
+    <t>Minggu 3</t>
+  </si>
+  <si>
+    <t>Satuan</t>
+  </si>
+  <si>
     <t>Keterangan</t>
   </si>
   <si>
+    <t>Demand / Pesanan (pcs)</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>Data permintaan / pesanan produksi</t>
+  </si>
+  <si>
+    <t>MPS / Produksi (pcs)</t>
+  </si>
+  <si>
+    <t>Rencana produksi = memenuhi demand</t>
+  </si>
+  <si>
+    <t>Keterangan / Rumus</t>
+  </si>
+  <si>
+    <t>GR</t>
+  </si>
+  <si>
+    <t>Gross Requirement
+(Kebutuhan Kotor)</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>GR = MPS × BOM = Produksi × 0,5 kg/pcs</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>Scheduled Receipts
+(Penerimaan Terjadwal)</t>
+  </si>
+  <si>
+    <t>PoH</t>
+  </si>
+  <si>
+    <t>Projected On Hand
+(Persediaan Awal Periode)</t>
+  </si>
+  <si>
+    <t>NR</t>
+  </si>
+  <si>
+    <t>Net Requirement
+(Kebutuhan Bersih)</t>
+  </si>
+  <si>
+    <t>PORt</t>
+  </si>
+  <si>
+    <t>Planned Order Receipt
+(Penerimaan Terencana)</t>
+  </si>
+  <si>
+    <t>PORel</t>
+  </si>
+  <si>
+    <t>Planned Order Release
+(Pelepasan Pesanan Terencana)</t>
+  </si>
+  <si>
+    <t>Minggu 4</t>
+  </si>
+  <si>
+    <t>Minggu 5</t>
+  </si>
+  <si>
+    <t>Minggu 6</t>
+  </si>
+  <si>
+    <t>Minggu 7</t>
+  </si>
+  <si>
+    <t>Minggu 0</t>
+  </si>
+  <si>
     <t>Quality</t>
   </si>
   <si>
@@ -352,6 +449,9 @@
   </si>
   <si>
     <t>DATA TOTAL PENGIRIMAN DELAY &amp; TEPAT WAKTU</t>
+  </si>
+  <si>
+    <t>MATERIAL REQUIREMENTS PLANNING (METODE LFL, LEAD TIME 1 MINGGU, DEFECT RATE 2.5%</t>
   </si>
   <si>
     <t>QUALITY CONTROL  DENGAN SNI AQL 2.5% DAN CHECKLIST 5 POINT INSPEKSI</t>
@@ -703,6 +803,28 @@
   </si>
   <si>
     <t xml:space="preserve">TAHAP 5: TEMPLATE PURCHASE ORDER &amp; QUALITY SPECIFICATION SHEET  </t>
+  </si>
+  <si>
+    <t>NR = GR - PoH − SR + SS, dengan syarat min 0</t>
+  </si>
+  <si>
+    <t>PORt M(t) = Jumlah barang yang masuk yang sudah direncanakan dengan LT = 1 minggu</t>
+  </si>
+  <si>
+    <t>SR =Bahan baku yang sudah di pesan/dijadwalkan tiba</t>
+  </si>
+  <si>
+    <t>PoH minggu ini = sisa stok minggu/periode kemarin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORel = NR (Lot-for-Lot); Pesanan yang dikirim ke supplier </t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>Komponen MRP
+LT: 1 minggu</t>
   </si>
   <si>
     <t>TAHAP 1: MENGIRIM TABEL RENCANA SAMPEL AQL 2,5</t>
@@ -754,7 +876,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -800,6 +922,12 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,6 +938,12 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1429,7 +1563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1495,6 +1629,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1524,7 +1667,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1567,7 +1710,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1587,22 +1730,55 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1794,6 +1970,24 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1812,64 +2006,139 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1879,111 +2148,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2084,7 +2248,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$BQ$19</c:f>
+              <c:f>Dasbord!$BQ$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2163,7 +2327,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$BO$20:$BO$22</c:f>
+              <c:f>Dasbord!$BO$20:$BO$22</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2180,7 +2344,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$BQ$20:$BQ$22</c:f>
+              <c:f>Dasbord!$BQ$20:$BQ$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2207,7 +2371,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$BR$19</c:f>
+              <c:f>Dasbord!$BR$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2286,7 +2450,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$BO$20:$BO$22</c:f>
+              <c:f>Dasbord!$BO$20:$BO$22</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2303,7 +2467,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$BR$20:$BR$22</c:f>
+              <c:f>Dasbord!$BR$20:$BR$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2803,7 +2967,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$BQ$29</c:f>
+              <c:f>Dasbord!$BQ$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2882,7 +3046,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$BP$30:$BP$32</c:f>
+              <c:f>Dasbord!$BP$30:$BP$32</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2899,7 +3063,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$BQ$30:$BQ$32</c:f>
+              <c:f>Dasbord!$BQ$30:$BQ$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -3296,7 +3460,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$BT$39</c:f>
+              <c:f>Dasbord!$BT$39</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3423,7 +3587,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$BP$40:$BP$42</c:f>
+              <c:f>Dasbord!$BP$40:$BP$42</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -3440,7 +3604,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$BT$40:$BT$42</c:f>
+              <c:f>Dasbord!$BT$40:$BT$42</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
@@ -3631,7 +3795,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$BQ$49</c:f>
+              <c:f>Dasbord!$BQ$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3710,7 +3874,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$BP$50:$BP$52</c:f>
+              <c:f>Dasbord!$BP$50:$BP$52</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -3727,7 +3891,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$BQ$50:$BQ$52</c:f>
+              <c:f>Dasbord!$BQ$50:$BQ$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -3754,7 +3918,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$BS$49</c:f>
+              <c:f>Dasbord!$BS$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3833,7 +3997,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$BP$50:$BP$52</c:f>
+              <c:f>Dasbord!$BP$50:$BP$52</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -3850,7 +4014,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$BS$50:$BS$52</c:f>
+              <c:f>Dasbord!$BS$50:$BS$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -6889,6 +7053,478 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B39F936-292A-4B05-9A44-FDA761ECAFC0}">
+  <dimension ref="B1:M16"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="8.7109375" style="23"/>
+    <col min="3" max="3" width="44.140625" style="23" customWidth="1"/>
+    <col min="4" max="6" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="23" customWidth="1"/>
+    <col min="8" max="11" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="43.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C2" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="78"/>
+    </row>
+    <row r="3" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="79"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="81"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="83"/>
+      <c r="D7" s="26">
+        <v>100</v>
+      </c>
+      <c r="E7" s="26">
+        <v>100</v>
+      </c>
+      <c r="F7" s="26">
+        <v>100</v>
+      </c>
+      <c r="G7" s="26">
+        <v>100</v>
+      </c>
+      <c r="H7" s="26">
+        <v>100</v>
+      </c>
+      <c r="I7" s="26">
+        <v>100</v>
+      </c>
+      <c r="J7" s="26">
+        <v>100</v>
+      </c>
+      <c r="K7" s="26">
+        <v>100</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="83"/>
+      <c r="D8" s="26">
+        <f t="shared" ref="D8:K8" si="0">D7</f>
+        <v>100</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F8" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="G8" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H8" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I8" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J8" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K8" s="26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="2:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="84" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="84"/>
+      <c r="D10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9">
+        <f>E8*0.5</f>
+        <v>50</v>
+      </c>
+      <c r="F11" s="9">
+        <f t="shared" ref="F11:K11" si="1">F8*0.5</f>
+        <v>50</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="H11" s="9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="J11" s="9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K11" s="9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" s="27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" s="27" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="9">
+        <v>20</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" ref="E13:K13" si="2">D13+E12+E15-E11</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" s="27" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9">
+        <f t="shared" ref="E14:K14" si="3">MAX(0,E11-(D13+E12))</f>
+        <v>20</v>
+      </c>
+      <c r="F14" s="9">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="G14" s="9">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="H14" s="9">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="J14" s="9">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="K14" s="9">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" s="27" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9">
+        <f>D16</f>
+        <v>20</v>
+      </c>
+      <c r="F15" s="9">
+        <f>E16</f>
+        <v>50</v>
+      </c>
+      <c r="G15" s="9">
+        <f t="shared" ref="G15:K15" si="4">F16</f>
+        <v>50</v>
+      </c>
+      <c r="H15" s="9">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="J15" s="9">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="L15" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="M15" s="27" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="9">
+        <f>E14</f>
+        <v>20</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" ref="E16:J16" si="5">F14</f>
+        <v>50</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" s="27" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:L3"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4B1EEE-8D2C-462F-98EF-DFD285E51E4E}">
   <dimension ref="B1:N94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -6907,338 +7543,338 @@
   <sheetData>
     <row r="1" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C2" s="39"/>
-      <c r="D2" s="120" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="122"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="136"/>
     </row>
     <row r="3" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="39"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="125"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="139"/>
     </row>
     <row r="4" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D5" s="126" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" s="127"/>
-      <c r="F5" s="128"/>
+      <c r="D5" s="140" t="s">
+        <v>256</v>
+      </c>
+      <c r="E5" s="141"/>
+      <c r="F5" s="142"/>
     </row>
     <row r="6" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="129"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="131"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="145"/>
     </row>
     <row r="7" spans="2:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
     </row>
     <row r="8" spans="2:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C8" s="18" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="38" t="s">
+      <c r="C9" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="38">
+      <c r="D9" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="41">
         <v>2</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="41">
         <v>0</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="41">
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="38" t="s">
+      <c r="C10" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="41">
         <v>3</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="41">
         <v>0</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="41">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" s="38">
+      <c r="C11" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="41">
         <v>5</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="41">
         <v>0</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="38">
+      <c r="C12" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="41">
         <v>8</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="41">
         <v>0</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="38">
+      <c r="C13" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="41">
         <v>13</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="41">
         <v>1</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="41">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="38">
+      <c r="C14" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="41">
         <v>20</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="41">
         <v>1</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="41">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="41">
         <v>32</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="41">
         <v>2</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="41">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="38">
+      <c r="C16" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="41">
         <v>50</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="41">
         <v>3</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="41">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="38">
+      <c r="C17" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="41">
         <v>80</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="41">
         <v>5</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="41">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C18" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="38">
+      <c r="C18" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="41">
         <v>125</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="41">
         <v>7</v>
       </c>
-      <c r="G18" s="38">
+      <c r="G18" s="41">
         <v>8</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="3:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C19" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" s="38">
+      <c r="C19" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="41">
         <v>200</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="41">
         <v>10</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="41">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C23" s="126" t="s">
-        <v>216</v>
-      </c>
-      <c r="D23" s="127"/>
-      <c r="E23" s="128"/>
+      <c r="C23" s="140" t="s">
+        <v>247</v>
+      </c>
+      <c r="D23" s="141"/>
+      <c r="E23" s="142"/>
     </row>
     <row r="24" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="129"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="131"/>
+      <c r="C24" s="143"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="145"/>
     </row>
     <row r="26" spans="3:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C26" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>122</v>
+      <c r="C26" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="3:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C27" s="25" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="3:9" ht="63" x14ac:dyDescent="0.25">
       <c r="C28" s="25" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="3:9" ht="63" x14ac:dyDescent="0.25">
       <c r="C29" s="25" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.25">
@@ -7249,154 +7885,154 @@
     </row>
     <row r="32" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C33" s="126" t="s">
-        <v>219</v>
-      </c>
-      <c r="D33" s="127"/>
-      <c r="E33" s="128"/>
+      <c r="C33" s="140" t="s">
+        <v>257</v>
+      </c>
+      <c r="D33" s="141"/>
+      <c r="E33" s="142"/>
     </row>
     <row r="34" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="129"/>
-      <c r="D34" s="130"/>
-      <c r="E34" s="131"/>
+      <c r="C34" s="143"/>
+      <c r="D34" s="144"/>
+      <c r="E34" s="145"/>
     </row>
     <row r="35" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>205</v>
+      <c r="C36" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="D36" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="D37" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="E37" s="44" t="s">
-        <v>208</v>
+      <c r="C37" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="E37" s="47" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="E38" s="44" t="s">
-        <v>139</v>
+      <c r="C38" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="44" t="s">
-        <v>142</v>
+      <c r="C39" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" s="47" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" s="44" t="s">
-        <v>192</v>
+      <c r="C40" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="D41" s="44" t="s">
+      <c r="C41" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="44" t="s">
-        <v>209</v>
+      <c r="E41" s="47" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="43" t="s">
+      <c r="C42" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="44" t="s">
-        <v>211</v>
+      <c r="D42" s="47" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="D43" s="44">
+      <c r="C43" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D43" s="47">
         <v>0</v>
       </c>
-      <c r="E43" s="44" t="s">
-        <v>212</v>
+      <c r="E43" s="47" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="3:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="D44" s="44">
+      <c r="C44" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="47">
         <v>1</v>
       </c>
-      <c r="E44" s="44" t="s">
-        <v>213</v>
+      <c r="E44" s="47" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="3:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="48" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D48" s="126" t="s">
-        <v>220</v>
-      </c>
-      <c r="E48" s="127"/>
-      <c r="F48" s="128"/>
+      <c r="D48" s="140" t="s">
+        <v>258</v>
+      </c>
+      <c r="E48" s="141"/>
+      <c r="F48" s="142"/>
     </row>
     <row r="49" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="129"/>
-      <c r="E49" s="130"/>
-      <c r="F49" s="131"/>
+      <c r="D49" s="143"/>
+      <c r="E49" s="144"/>
+      <c r="F49" s="145"/>
     </row>
     <row r="51" spans="3:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C51" s="24" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="G51" s="70" t="s">
-        <v>151</v>
-      </c>
-      <c r="H51" s="70"/>
+        <v>181</v>
+      </c>
+      <c r="G51" s="84" t="s">
+        <v>182</v>
+      </c>
+      <c r="H51" s="84"/>
     </row>
     <row r="52" spans="3:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C52" s="25" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E52" s="25" t="s">
         <v>54</v>
@@ -7404,122 +8040,122 @@
       <c r="F52" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="G52" s="69" t="s">
-        <v>155</v>
-      </c>
-      <c r="H52" s="69"/>
+      <c r="G52" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="83"/>
     </row>
     <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="25" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="G53" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="H53" s="69"/>
+        <v>190</v>
+      </c>
+      <c r="G53" s="83" t="s">
+        <v>191</v>
+      </c>
+      <c r="H53" s="83"/>
     </row>
     <row r="54" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C54" s="25" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="G54" s="69" t="s">
-        <v>165</v>
-      </c>
-      <c r="H54" s="69"/>
+        <v>195</v>
+      </c>
+      <c r="G54" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="H54" s="83"/>
     </row>
     <row r="55" spans="3:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C55" s="25" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G55" s="69" t="s">
-        <v>168</v>
-      </c>
-      <c r="H55" s="69"/>
+        <v>185</v>
+      </c>
+      <c r="G55" s="83" t="s">
+        <v>199</v>
+      </c>
+      <c r="H55" s="83"/>
     </row>
     <row r="56" spans="3:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C56" s="25" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G56" s="69" t="s">
-        <v>172</v>
-      </c>
-      <c r="H56" s="69"/>
+        <v>185</v>
+      </c>
+      <c r="G56" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="H56" s="83"/>
     </row>
     <row r="57" spans="3:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C57" s="25" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G57" s="69" t="s">
-        <v>175</v>
-      </c>
-      <c r="H57" s="69"/>
+        <v>185</v>
+      </c>
+      <c r="G57" s="83" t="s">
+        <v>206</v>
+      </c>
+      <c r="H57" s="83"/>
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="I60" s="2" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
     </row>
     <row r="61" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="D62" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="E62" s="121"/>
-      <c r="F62" s="121"/>
-      <c r="G62" s="121"/>
-      <c r="H62" s="122"/>
+      <c r="D62" s="134" t="s">
+        <v>248</v>
+      </c>
+      <c r="E62" s="135"/>
+      <c r="F62" s="135"/>
+      <c r="G62" s="135"/>
+      <c r="H62" s="136"/>
     </row>
     <row r="63" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D63" s="123"/>
-      <c r="E63" s="124"/>
-      <c r="F63" s="124"/>
-      <c r="G63" s="124"/>
-      <c r="H63" s="125"/>
+      <c r="D63" s="137"/>
+      <c r="E63" s="138"/>
+      <c r="F63" s="138"/>
+      <c r="G63" s="138"/>
+      <c r="H63" s="139"/>
     </row>
     <row r="64" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C64" s="23"/>
@@ -7536,352 +8172,352 @@
       <c r="N64" s="23"/>
     </row>
     <row r="65" spans="3:9" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="114" t="s">
-        <v>176</v>
-      </c>
-      <c r="D65" s="115"/>
-      <c r="E65" s="115"/>
-      <c r="F65" s="115"/>
-      <c r="G65" s="115"/>
-      <c r="H65" s="115"/>
-      <c r="I65" s="116"/>
+      <c r="C65" s="128" t="s">
+        <v>207</v>
+      </c>
+      <c r="D65" s="129"/>
+      <c r="E65" s="129"/>
+      <c r="F65" s="129"/>
+      <c r="G65" s="129"/>
+      <c r="H65" s="129"/>
+      <c r="I65" s="130"/>
     </row>
     <row r="66" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C66" s="79" t="s">
-        <v>177</v>
-      </c>
-      <c r="D66" s="80"/>
-      <c r="E66" s="81"/>
-      <c r="F66" s="82" t="s">
-        <v>178</v>
-      </c>
-      <c r="G66" s="83"/>
-      <c r="H66" s="83"/>
-      <c r="I66" s="84"/>
+      <c r="C66" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="D66" s="94"/>
+      <c r="E66" s="95"/>
+      <c r="F66" s="96" t="s">
+        <v>209</v>
+      </c>
+      <c r="G66" s="97"/>
+      <c r="H66" s="97"/>
+      <c r="I66" s="98"/>
     </row>
     <row r="67" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C67" s="71" t="s">
-        <v>179</v>
-      </c>
-      <c r="D67" s="72"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="85">
+      <c r="C67" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="D67" s="86"/>
+      <c r="E67" s="87"/>
+      <c r="F67" s="99">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
-      </c>
-      <c r="G67" s="86"/>
-      <c r="H67" s="86"/>
-      <c r="I67" s="87"/>
+        <v>46220</v>
+      </c>
+      <c r="G67" s="100"/>
+      <c r="H67" s="100"/>
+      <c r="I67" s="101"/>
     </row>
     <row r="68" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C68" s="71" t="s">
+      <c r="C68" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="D68" s="72"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="74" t="s">
-        <v>180</v>
-      </c>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
-      <c r="I68" s="76"/>
+      <c r="D68" s="86"/>
+      <c r="E68" s="87"/>
+      <c r="F68" s="88" t="s">
+        <v>211</v>
+      </c>
+      <c r="G68" s="89"/>
+      <c r="H68" s="89"/>
+      <c r="I68" s="90"/>
     </row>
     <row r="69" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="71" t="s">
-        <v>181</v>
-      </c>
-      <c r="D69" s="72"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="74" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69" s="75"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="76"/>
+      <c r="C69" s="85" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" s="86"/>
+      <c r="E69" s="87"/>
+      <c r="F69" s="88" t="s">
+        <v>213</v>
+      </c>
+      <c r="G69" s="89"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="90"/>
     </row>
     <row r="70" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="71" t="s">
-        <v>183</v>
-      </c>
-      <c r="D70" s="72"/>
-      <c r="E70" s="73"/>
-      <c r="F70" s="77">
+      <c r="C70" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="D70" s="86"/>
+      <c r="E70" s="87"/>
+      <c r="F70" s="91">
         <v>15</v>
       </c>
-      <c r="G70" s="69"/>
-      <c r="H70" s="72" t="s">
-        <v>184</v>
-      </c>
-      <c r="I70" s="78"/>
+      <c r="G70" s="83"/>
+      <c r="H70" s="86" t="s">
+        <v>215</v>
+      </c>
+      <c r="I70" s="92"/>
     </row>
     <row r="71" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C71" s="71" t="s">
-        <v>185</v>
-      </c>
-      <c r="D71" s="72"/>
-      <c r="E71" s="73"/>
-      <c r="F71" s="77">
+      <c r="C71" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="D71" s="86"/>
+      <c r="E71" s="87"/>
+      <c r="F71" s="91">
         <v>75000</v>
       </c>
-      <c r="G71" s="69"/>
-      <c r="H71" s="72" t="s">
-        <v>186</v>
-      </c>
-      <c r="I71" s="78"/>
+      <c r="G71" s="83"/>
+      <c r="H71" s="86" t="s">
+        <v>217</v>
+      </c>
+      <c r="I71" s="92"/>
     </row>
     <row r="72" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="89" t="s">
-        <v>187</v>
-      </c>
-      <c r="D72" s="90"/>
-      <c r="E72" s="91"/>
-      <c r="F72" s="92">
+      <c r="C72" s="103" t="s">
+        <v>218</v>
+      </c>
+      <c r="D72" s="104"/>
+      <c r="E72" s="105"/>
+      <c r="F72" s="106">
         <f>F70*F71</f>
         <v>1125000</v>
       </c>
-      <c r="G72" s="93"/>
-      <c r="H72" s="93"/>
-      <c r="I72" s="94"/>
+      <c r="G72" s="107"/>
+      <c r="H72" s="107"/>
+      <c r="I72" s="108"/>
     </row>
     <row r="73" spans="3:9" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="114" t="s">
-        <v>188</v>
-      </c>
-      <c r="D73" s="115"/>
-      <c r="E73" s="115"/>
-      <c r="F73" s="115"/>
-      <c r="G73" s="115"/>
-      <c r="H73" s="115"/>
-      <c r="I73" s="116"/>
+      <c r="C73" s="128" t="s">
+        <v>219</v>
+      </c>
+      <c r="D73" s="129"/>
+      <c r="E73" s="129"/>
+      <c r="F73" s="129"/>
+      <c r="G73" s="129"/>
+      <c r="H73" s="129"/>
+      <c r="I73" s="130"/>
     </row>
     <row r="74" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C74" s="79" t="s">
-        <v>189</v>
-      </c>
-      <c r="D74" s="80"/>
-      <c r="E74" s="88"/>
-      <c r="F74" s="82" t="s">
-        <v>190</v>
-      </c>
-      <c r="G74" s="83"/>
-      <c r="H74" s="83"/>
-      <c r="I74" s="84"/>
+      <c r="C74" s="93" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" s="94"/>
+      <c r="E74" s="102"/>
+      <c r="F74" s="96" t="s">
+        <v>221</v>
+      </c>
+      <c r="G74" s="97"/>
+      <c r="H74" s="97"/>
+      <c r="I74" s="98"/>
     </row>
     <row r="75" spans="3:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="71" t="s">
-        <v>144</v>
-      </c>
-      <c r="D75" s="72"/>
-      <c r="E75" s="78"/>
-      <c r="F75" s="74" t="s">
-        <v>191</v>
-      </c>
-      <c r="G75" s="75"/>
-      <c r="H75" s="75"/>
-      <c r="I75" s="76"/>
+      <c r="C75" s="85" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" s="86"/>
+      <c r="E75" s="92"/>
+      <c r="F75" s="88" t="s">
+        <v>222</v>
+      </c>
+      <c r="G75" s="89"/>
+      <c r="H75" s="89"/>
+      <c r="I75" s="90"/>
     </row>
     <row r="76" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C76" s="71" t="s">
-        <v>137</v>
-      </c>
-      <c r="D76" s="72"/>
-      <c r="E76" s="78"/>
-      <c r="F76" s="74" t="s">
-        <v>193</v>
-      </c>
-      <c r="G76" s="75"/>
-      <c r="H76" s="75"/>
-      <c r="I76" s="76"/>
+      <c r="C76" s="85" t="s">
+        <v>168</v>
+      </c>
+      <c r="D76" s="86"/>
+      <c r="E76" s="92"/>
+      <c r="F76" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="G76" s="89"/>
+      <c r="H76" s="89"/>
+      <c r="I76" s="90"/>
     </row>
     <row r="77" spans="3:9" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="89" t="s">
-        <v>194</v>
-      </c>
-      <c r="D77" s="90"/>
-      <c r="E77" s="113"/>
-      <c r="F77" s="117" t="str">
+      <c r="C77" s="103" t="s">
+        <v>225</v>
+      </c>
+      <c r="D77" s="104"/>
+      <c r="E77" s="127"/>
+      <c r="F77" s="131" t="str">
         <f>IF(F70&lt;=8,"Kode A: n=2, Ac=0, Re=1",IF(F70&lt;=15,"Kode B: n=3, Ac=0, Re=1",IF(F70&lt;=25,"Kode C: n=5, Ac=0, Re=1",IF(F70&lt;=50,"Kode D: n=8, Ac=0, Re=1",IF(F70&lt;=90,"Kode E: n=13, Ac=1, Re=2",IF(F70&lt;=150,"Kode F: n=20, Ac=1, Re=2",IF(F70&lt;=280,"Kode G: n=32, Ac=2, Re=3",IF(F70&lt;=500,"Kode H: n=50, Ac=3, Re=4",IF(F70&lt;=1200,"Kode J: n=80, Ac=5, Re=6",IF(F70&lt;=3200,"Kode K: n=125, Ac=7, Re=8","Kode L: n=200, Ac=10, Re=11"))))))))))</f>
         <v>Kode B: n=3, Ac=0, Re=1</v>
       </c>
-      <c r="G77" s="118"/>
-      <c r="H77" s="118"/>
-      <c r="I77" s="119"/>
+      <c r="G77" s="132"/>
+      <c r="H77" s="132"/>
+      <c r="I77" s="133"/>
     </row>
     <row r="78" spans="3:9" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="114" t="s">
-        <v>195</v>
-      </c>
-      <c r="D78" s="115"/>
-      <c r="E78" s="115"/>
-      <c r="F78" s="115"/>
-      <c r="G78" s="115"/>
-      <c r="H78" s="115"/>
-      <c r="I78" s="116"/>
+      <c r="C78" s="128" t="s">
+        <v>226</v>
+      </c>
+      <c r="D78" s="129"/>
+      <c r="E78" s="129"/>
+      <c r="F78" s="129"/>
+      <c r="G78" s="129"/>
+      <c r="H78" s="129"/>
+      <c r="I78" s="130"/>
     </row>
     <row r="79" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C79" s="79" t="s">
-        <v>156</v>
-      </c>
-      <c r="D79" s="80"/>
-      <c r="E79" s="88"/>
-      <c r="F79" s="79" t="s">
-        <v>196</v>
-      </c>
-      <c r="G79" s="88"/>
-      <c r="H79" s="79" t="s">
+      <c r="C79" s="93" t="s">
+        <v>187</v>
+      </c>
+      <c r="D79" s="94"/>
+      <c r="E79" s="102"/>
+      <c r="F79" s="93" t="s">
+        <v>227</v>
+      </c>
+      <c r="G79" s="102"/>
+      <c r="H79" s="93" t="s">
+        <v>228</v>
+      </c>
+      <c r="I79" s="102"/>
+    </row>
+    <row r="80" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C80" s="85" t="s">
+        <v>192</v>
+      </c>
+      <c r="D80" s="86"/>
+      <c r="E80" s="92"/>
+      <c r="F80" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="G80" s="92"/>
+      <c r="H80" s="85" t="s">
+        <v>230</v>
+      </c>
+      <c r="I80" s="92"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C81" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="I79" s="88"/>
-    </row>
-    <row r="80" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C80" s="71" t="s">
-        <v>161</v>
-      </c>
-      <c r="D80" s="72"/>
-      <c r="E80" s="78"/>
-      <c r="F80" s="71" t="s">
+      <c r="D81" s="86"/>
+      <c r="E81" s="92"/>
+      <c r="F81" s="85" t="s">
         <v>198</v>
       </c>
-      <c r="G80" s="78"/>
-      <c r="H80" s="71" t="s">
-        <v>199</v>
-      </c>
-      <c r="I80" s="78"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C81" s="71" t="s">
-        <v>166</v>
-      </c>
-      <c r="D81" s="72"/>
-      <c r="E81" s="78"/>
-      <c r="F81" s="71" t="s">
-        <v>167</v>
-      </c>
-      <c r="G81" s="78"/>
-      <c r="H81" s="71" t="s">
-        <v>200</v>
-      </c>
-      <c r="I81" s="78"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="I81" s="92"/>
     </row>
     <row r="82" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C82" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="D82" s="90"/>
-      <c r="E82" s="113"/>
-      <c r="F82" s="89" t="s">
-        <v>201</v>
-      </c>
-      <c r="G82" s="113"/>
-      <c r="H82" s="89" t="s">
-        <v>202</v>
-      </c>
-      <c r="I82" s="113"/>
+      <c r="C82" s="103" t="s">
+        <v>204</v>
+      </c>
+      <c r="D82" s="104"/>
+      <c r="E82" s="127"/>
+      <c r="F82" s="103" t="s">
+        <v>232</v>
+      </c>
+      <c r="G82" s="127"/>
+      <c r="H82" s="103" t="s">
+        <v>233</v>
+      </c>
+      <c r="I82" s="127"/>
     </row>
     <row r="83" spans="3:14" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C83" s="114" t="s">
-        <v>203</v>
-      </c>
-      <c r="D83" s="115"/>
-      <c r="E83" s="115"/>
-      <c r="F83" s="115"/>
-      <c r="G83" s="115"/>
-      <c r="H83" s="115"/>
-      <c r="I83" s="116"/>
+      <c r="C83" s="128" t="s">
+        <v>234</v>
+      </c>
+      <c r="D83" s="129"/>
+      <c r="E83" s="129"/>
+      <c r="F83" s="129"/>
+      <c r="G83" s="129"/>
+      <c r="H83" s="129"/>
+      <c r="I83" s="130"/>
     </row>
     <row r="84" spans="3:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C84" s="95" t="s">
-        <v>214</v>
-      </c>
-      <c r="D84" s="96"/>
-      <c r="E84" s="97"/>
-      <c r="F84" s="104" t="s">
-        <v>215</v>
-      </c>
-      <c r="G84" s="105"/>
-      <c r="H84" s="105"/>
-      <c r="I84" s="106"/>
+      <c r="C84" s="109" t="s">
+        <v>245</v>
+      </c>
+      <c r="D84" s="110"/>
+      <c r="E84" s="111"/>
+      <c r="F84" s="118" t="s">
+        <v>246</v>
+      </c>
+      <c r="G84" s="119"/>
+      <c r="H84" s="119"/>
+      <c r="I84" s="120"/>
     </row>
     <row r="85" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C85" s="98"/>
-      <c r="D85" s="99"/>
-      <c r="E85" s="100"/>
-      <c r="F85" s="107"/>
-      <c r="G85" s="108"/>
-      <c r="H85" s="108"/>
-      <c r="I85" s="109"/>
+      <c r="C85" s="112"/>
+      <c r="D85" s="113"/>
+      <c r="E85" s="114"/>
+      <c r="F85" s="121"/>
+      <c r="G85" s="122"/>
+      <c r="H85" s="122"/>
+      <c r="I85" s="123"/>
     </row>
     <row r="86" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C86" s="98"/>
-      <c r="D86" s="99"/>
-      <c r="E86" s="100"/>
-      <c r="F86" s="107"/>
-      <c r="G86" s="108"/>
-      <c r="H86" s="108"/>
-      <c r="I86" s="109"/>
+      <c r="C86" s="112"/>
+      <c r="D86" s="113"/>
+      <c r="E86" s="114"/>
+      <c r="F86" s="121"/>
+      <c r="G86" s="122"/>
+      <c r="H86" s="122"/>
+      <c r="I86" s="123"/>
     </row>
     <row r="87" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C87" s="98"/>
-      <c r="D87" s="99"/>
-      <c r="E87" s="100"/>
-      <c r="F87" s="107"/>
-      <c r="G87" s="108"/>
-      <c r="H87" s="108"/>
-      <c r="I87" s="109"/>
+      <c r="C87" s="112"/>
+      <c r="D87" s="113"/>
+      <c r="E87" s="114"/>
+      <c r="F87" s="121"/>
+      <c r="G87" s="122"/>
+      <c r="H87" s="122"/>
+      <c r="I87" s="123"/>
     </row>
     <row r="88" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C88" s="98"/>
-      <c r="D88" s="99"/>
-      <c r="E88" s="100"/>
-      <c r="F88" s="107"/>
-      <c r="G88" s="108"/>
-      <c r="H88" s="108"/>
-      <c r="I88" s="109"/>
+      <c r="C88" s="112"/>
+      <c r="D88" s="113"/>
+      <c r="E88" s="114"/>
+      <c r="F88" s="121"/>
+      <c r="G88" s="122"/>
+      <c r="H88" s="122"/>
+      <c r="I88" s="123"/>
     </row>
     <row r="89" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C89" s="98"/>
-      <c r="D89" s="99"/>
-      <c r="E89" s="100"/>
-      <c r="F89" s="107"/>
-      <c r="G89" s="108"/>
-      <c r="H89" s="108"/>
-      <c r="I89" s="109"/>
+      <c r="C89" s="112"/>
+      <c r="D89" s="113"/>
+      <c r="E89" s="114"/>
+      <c r="F89" s="121"/>
+      <c r="G89" s="122"/>
+      <c r="H89" s="122"/>
+      <c r="I89" s="123"/>
     </row>
     <row r="90" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C90" s="98"/>
-      <c r="D90" s="99"/>
-      <c r="E90" s="100"/>
-      <c r="F90" s="107"/>
-      <c r="G90" s="108"/>
-      <c r="H90" s="108"/>
-      <c r="I90" s="109"/>
+      <c r="C90" s="112"/>
+      <c r="D90" s="113"/>
+      <c r="E90" s="114"/>
+      <c r="F90" s="121"/>
+      <c r="G90" s="122"/>
+      <c r="H90" s="122"/>
+      <c r="I90" s="123"/>
     </row>
     <row r="91" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C91" s="98"/>
-      <c r="D91" s="99"/>
-      <c r="E91" s="100"/>
-      <c r="F91" s="107"/>
-      <c r="G91" s="108"/>
-      <c r="H91" s="108"/>
-      <c r="I91" s="109"/>
+      <c r="C91" s="112"/>
+      <c r="D91" s="113"/>
+      <c r="E91" s="114"/>
+      <c r="F91" s="121"/>
+      <c r="G91" s="122"/>
+      <c r="H91" s="122"/>
+      <c r="I91" s="123"/>
     </row>
     <row r="92" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C92" s="98"/>
-      <c r="D92" s="99"/>
-      <c r="E92" s="100"/>
-      <c r="F92" s="107"/>
-      <c r="G92" s="108"/>
-      <c r="H92" s="108"/>
-      <c r="I92" s="109"/>
+      <c r="C92" s="112"/>
+      <c r="D92" s="113"/>
+      <c r="E92" s="114"/>
+      <c r="F92" s="121"/>
+      <c r="G92" s="122"/>
+      <c r="H92" s="122"/>
+      <c r="I92" s="123"/>
     </row>
     <row r="93" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C93" s="101"/>
-      <c r="D93" s="102"/>
-      <c r="E93" s="103"/>
-      <c r="F93" s="110"/>
-      <c r="G93" s="111"/>
-      <c r="H93" s="111"/>
-      <c r="I93" s="112"/>
+      <c r="C93" s="115"/>
+      <c r="D93" s="116"/>
+      <c r="E93" s="117"/>
+      <c r="F93" s="124"/>
+      <c r="G93" s="125"/>
+      <c r="H93" s="125"/>
+      <c r="I93" s="126"/>
       <c r="J93" s="23"/>
       <c r="K93" s="23"/>
       <c r="L93" s="23"/>
@@ -7964,7 +8600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13887B3D-ABA6-40F5-9562-D7EADADD5B53}">
   <dimension ref="B1:AH40"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -8005,30 +8641,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="F1" s="63" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="65"/>
+      <c r="F1" s="146" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="148"/>
     </row>
     <row r="2" spans="2:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="68"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="150"/>
+      <c r="O2" s="151"/>
     </row>
     <row r="4" spans="2:34" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
@@ -8079,17 +8715,17 @@
       <c r="Q4" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="S4" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="T4" s="36" t="s">
-        <v>94</v>
+      <c r="R4" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="S4" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="T4" s="39" t="s">
+        <v>124</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.25">
@@ -8112,7 +8748,7 @@
         <v>8</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I29" si="0">IF(H5="","",IFERROR(VLOOKUP(H5,$AD$6:$AF$17,2,0),"?"))</f>
@@ -8122,7 +8758,7 @@
         <f t="shared" ref="J5:J29" si="1">IF(H5="","",IFERROR(VLOOKUP(H5,$AD$6:$AF$17,3,0),"?"))</f>
         <v>2</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="48">
         <v>1</v>
       </c>
       <c r="L5" s="9" t="s">
@@ -8145,7 +8781,7 @@
         <v>51</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="S5" s="1" t="str">
         <f>C5</f>
@@ -8178,7 +8814,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
@@ -8188,7 +8824,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="48">
         <v>0</v>
       </c>
       <c r="L6" s="9" t="s">
@@ -8211,7 +8847,7 @@
         <v>29</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="S6" s="1" t="str">
         <f>C6</f>
@@ -8223,15 +8859,15 @@
       </c>
       <c r="U6" s="1"/>
       <c r="Z6" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA6" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA6" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AB6" s="31" t="s">
+      <c r="AB6" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="AC6" s="31" t="s">
+      <c r="AC6" s="34" t="s">
         <v>3</v>
       </c>
       <c r="AD6" s="14" t="s">
@@ -8243,10 +8879,10 @@
       <c r="AF6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="AG6" s="32" t="s">
+      <c r="AG6" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AH6" s="32" t="s">
+      <c r="AH6" s="35" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8271,7 +8907,7 @@
         <v>20</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="0"/>
@@ -8281,7 +8917,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K7" s="45">
+      <c r="K7" s="48">
         <v>2</v>
       </c>
       <c r="L7" s="9" t="s">
@@ -8304,7 +8940,7 @@
         <v>51</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="S7" s="1" t="str">
         <f t="shared" ref="S7:S10" si="5">C7</f>
@@ -8316,19 +8952,19 @@
       </c>
       <c r="U7" s="1"/>
       <c r="Z7" s="15" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="AA7" s="15">
         <v>2</v>
       </c>
-      <c r="AB7" s="30" t="s">
+      <c r="AB7" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="AC7" s="30" t="s">
+      <c r="AC7" s="33" t="s">
         <v>10</v>
       </c>
       <c r="AD7" s="15" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AE7" s="15">
         <v>0</v>
@@ -8362,7 +8998,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="0"/>
@@ -8372,7 +9008,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K8" s="45">
+      <c r="K8" s="48">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="s">
@@ -8407,15 +9043,15 @@
       </c>
       <c r="U8" s="1"/>
       <c r="Z8" s="15" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="AA8" s="15">
         <v>3</v>
       </c>
-      <c r="AB8" s="30" t="s">
+      <c r="AB8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AC8" s="30" t="s">
+      <c r="AC8" s="33" t="s">
         <v>11</v>
       </c>
       <c r="AD8" s="15" t="s">
@@ -8453,7 +9089,7 @@
         <v>50</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="0"/>
@@ -8463,7 +9099,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K9" s="45">
+      <c r="K9" s="48">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -8498,19 +9134,19 @@
       </c>
       <c r="U9" s="1"/>
       <c r="Z9" s="15" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="AA9" s="15">
         <v>5</v>
       </c>
-      <c r="AB9" s="30" t="s">
+      <c r="AB9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="AC9" s="30" t="s">
+      <c r="AC9" s="33" t="s">
         <v>13</v>
       </c>
       <c r="AD9" s="15" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="AE9" s="15">
         <v>0</v>
@@ -8552,7 +9188,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K10" s="45">
+      <c r="K10" s="48">
         <v>20</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -8587,7 +9223,7 @@
       </c>
       <c r="U10" s="1"/>
       <c r="Z10" s="15" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AA10" s="15">
         <v>8</v>
@@ -8595,7 +9231,7 @@
       <c r="AB10" s="20"/>
       <c r="AC10" s="20"/>
       <c r="AD10" s="15" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="AE10" s="15">
         <v>0</v>
@@ -8607,40 +9243,40 @@
       <c r="AH10" s="20"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B11" s="46">
+      <c r="B11" s="49">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46" t="str">
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J11" s="46" t="str">
+      <c r="J11" s="49" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="47" t="str">
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="50" t="str">
         <f t="shared" ref="M11:M29" si="6">IF(K11="","",IF(K11&lt;=I11,"LOLOS",IF(K11&gt;=J11,"RETUR","HOLD")))</f>
         <v/>
       </c>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
       <c r="Z11" s="15" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="AA11" s="15">
         <v>13</v>
@@ -8648,7 +9284,7 @@
       <c r="AB11" s="20"/>
       <c r="AC11" s="20"/>
       <c r="AD11" s="15" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="AE11" s="15">
         <v>1</v>
@@ -8693,7 +9329,7 @@
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="Z12" s="15" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="AA12" s="15">
         <v>20</v>
@@ -8701,7 +9337,7 @@
       <c r="AB12" s="20"/>
       <c r="AC12" s="20"/>
       <c r="AD12" s="15" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="AE12" s="15">
         <v>1</v>
@@ -8746,7 +9382,7 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="Z13" s="15" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="AA13" s="15">
         <v>32</v>
@@ -8799,7 +9435,7 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="Z14" s="15" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="AA14" s="15">
         <v>50</v>
@@ -8807,7 +9443,7 @@
       <c r="AB14" s="20"/>
       <c r="AC14" s="20"/>
       <c r="AD14" s="15" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="AE14" s="15">
         <v>3</v>
@@ -8852,7 +9488,7 @@
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="Z15" s="15" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="AA15" s="15">
         <v>80</v>
@@ -8860,7 +9496,7 @@
       <c r="AB15" s="20"/>
       <c r="AC15" s="20"/>
       <c r="AD15" s="15" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="AE15" s="15">
         <v>5</v>
@@ -8905,7 +9541,7 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="Z16" s="15" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AA16" s="15">
         <v>125</v>
@@ -8913,7 +9549,7 @@
       <c r="AB16" s="20"/>
       <c r="AC16" s="20"/>
       <c r="AD16" s="15" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AE16" s="15">
         <v>7</v>
@@ -8958,7 +9594,7 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="Z17" s="15" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="AA17" s="15">
         <v>200</v>
@@ -8966,7 +9602,7 @@
       <c r="AB17" s="20"/>
       <c r="AC17" s="20"/>
       <c r="AD17" s="15" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AE17" s="15">
         <v>10</v>
@@ -9417,7 +10053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1534881D-0B0F-41D5-9E46-78590B8DAFDD}">
   <dimension ref="B1:O23"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -9445,26 +10081,26 @@
   <sheetData>
     <row r="1" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="65"/>
+      <c r="D2" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="148"/>
     </row>
     <row r="3" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="68"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="151"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
@@ -9791,7 +10427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F014A1-179D-4536-955C-726FEFEB8065}">
   <dimension ref="B2:N9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -9814,31 +10450,31 @@
   <sheetData>
     <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="35"/>
-      <c r="C3" s="132" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="134"/>
-      <c r="K3" s="138" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="140"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="152" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="153"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="153"/>
+      <c r="G3" s="154"/>
+      <c r="K3" s="158" t="s">
+        <v>132</v>
+      </c>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="137"/>
-      <c r="K4" s="141"/>
-      <c r="L4" s="142"/>
-      <c r="M4" s="142"/>
-      <c r="N4" s="143"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="157"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="163"/>
     </row>
     <row r="6" spans="2:14" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
@@ -9848,7 +10484,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E6" s="24" t="s">
         <v>55</v>
@@ -9865,14 +10501,14 @@
       <c r="K6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="M6" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="N6" s="36" t="s">
-        <v>101</v>
+      <c r="L6" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="M6" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="N6" s="39" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -10013,60 +10649,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3423FA21-9284-4F38-879B-2539DE9C91F3}">
   <dimension ref="D3:L25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="27"/>
-    <col min="2" max="2" width="17.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="27"/>
-    <col min="13" max="13" width="9" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="27"/>
+    <col min="1" max="1" width="8.7109375" style="30"/>
+    <col min="2" max="2" width="17.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="30"/>
+    <col min="13" max="13" width="9" style="30" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="30"/>
   </cols>
   <sheetData>
     <row r="3" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="E4" s="144" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="146"/>
+      <c r="E4" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="68"/>
     </row>
     <row r="5" spans="4:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="147"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="149"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="71"/>
     </row>
     <row r="7" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>69</v>
+      <c r="E7" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="4:9" x14ac:dyDescent="0.25">
@@ -10081,15 +10717,15 @@
         <f>'ADMINISTRASI DEFECT'!H7</f>
         <v>1</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="36">
         <f>'ADMINISTRASI DEFECT'!L7</f>
         <v>2</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="36">
         <f>'ADMINISTRASI DEFECT'!N7</f>
         <v>2</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="37">
         <v>75</v>
       </c>
     </row>
@@ -10105,15 +10741,15 @@
         <f>'ADMINISTRASI DEFECT'!H8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="36">
         <f>'ADMINISTRASI DEFECT'!M8</f>
         <v>1</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="36">
         <f>'ADMINISTRASI DEFECT'!N8</f>
         <v>1</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="37">
         <v>73</v>
       </c>
     </row>
@@ -10129,63 +10765,63 @@
         <f>'ADMINISTRASI DEFECT'!H9</f>
         <v>2</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="36">
         <f>'ADMINISTRASI DEFECT'!M9</f>
         <v>2</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="36">
         <f>'ADMINISTRASI DEFECT'!N9</f>
         <v>0</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="37">
         <v>72</v>
       </c>
     </row>
     <row r="18" spans="4:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="144" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="145"/>
-      <c r="G19" s="145"/>
-      <c r="H19" s="146"/>
-      <c r="K19" s="150" t="s">
-        <v>107</v>
-      </c>
-      <c r="L19" s="151"/>
+      <c r="E19" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="68"/>
+      <c r="K19" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" s="73"/>
     </row>
     <row r="20" spans="4:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="147"/>
-      <c r="F20" s="148"/>
-      <c r="G20" s="148"/>
-      <c r="H20" s="149"/>
-      <c r="K20" s="152"/>
-      <c r="L20" s="153"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="71"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="75"/>
     </row>
     <row r="22" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D22" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="K22" s="9" t="str">
         <f>E22</f>
         <v>Quality</v>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="32">
         <v>0.5</v>
       </c>
     </row>
@@ -10194,7 +10830,7 @@
         <f>D8</f>
         <v>Vendor A</v>
       </c>
-      <c r="E23" s="37">
+      <c r="E23" s="40">
         <f>((E8-F8)/E8)*100</f>
         <v>50</v>
       </c>
@@ -10218,7 +10854,7 @@
         <f>F22</f>
         <v>Delivery</v>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="32">
         <v>0.3</v>
       </c>
     </row>
@@ -10227,7 +10863,7 @@
         <f>D9</f>
         <v>Vendor B</v>
       </c>
-      <c r="E24" s="37">
+      <c r="E24" s="40">
         <f>((E9-F9)/E9)*100</f>
         <v>100</v>
       </c>
@@ -10235,11 +10871,11 @@
         <f>((H9/G9)*100)</f>
         <v>100</v>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="40">
         <f>((I10/I9)*100)</f>
         <v>98.630136986301366</v>
       </c>
-      <c r="H24" s="37">
+      <c r="H24" s="40">
         <f>(E24*L22)+(F24*L23)+(G24*L24)</f>
         <v>99.726027397260282</v>
       </c>
@@ -10251,7 +10887,7 @@
         <f>G22</f>
         <v>Price</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="32">
         <v>0.2</v>
       </c>
     </row>
@@ -10260,7 +10896,7 @@
         <f>D10</f>
         <v>Vendor C</v>
       </c>
-      <c r="E25" s="37">
+      <c r="E25" s="40">
         <f>((E10-F10)/E10)*100</f>
         <v>0</v>
       </c>
@@ -10291,7 +10927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFF980D-7AE5-429A-849F-FA28295604D6}">
   <dimension ref="E4:BU121"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -10316,282 +10952,282 @@
   <sheetData>
     <row r="4" spans="5:38" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="K5" s="161" t="s">
-        <v>232</v>
-      </c>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
-      <c r="O5" s="162"/>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="162"/>
-      <c r="R5" s="162"/>
-      <c r="S5" s="162"/>
-      <c r="T5" s="162"/>
-      <c r="U5" s="162"/>
-      <c r="V5" s="162"/>
-      <c r="W5" s="162"/>
-      <c r="X5" s="162"/>
-      <c r="Y5" s="162"/>
-      <c r="Z5" s="162"/>
-      <c r="AA5" s="162"/>
-      <c r="AB5" s="162"/>
-      <c r="AC5" s="162"/>
-      <c r="AD5" s="163"/>
+      <c r="K5" s="164" t="s">
+        <v>270</v>
+      </c>
+      <c r="L5" s="165"/>
+      <c r="M5" s="165"/>
+      <c r="N5" s="165"/>
+      <c r="O5" s="165"/>
+      <c r="P5" s="165"/>
+      <c r="Q5" s="165"/>
+      <c r="R5" s="165"/>
+      <c r="S5" s="165"/>
+      <c r="T5" s="165"/>
+      <c r="U5" s="165"/>
+      <c r="V5" s="165"/>
+      <c r="W5" s="165"/>
+      <c r="X5" s="165"/>
+      <c r="Y5" s="165"/>
+      <c r="Z5" s="165"/>
+      <c r="AA5" s="165"/>
+      <c r="AB5" s="165"/>
+      <c r="AC5" s="165"/>
+      <c r="AD5" s="166"/>
     </row>
     <row r="6" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="K6" s="164"/>
-      <c r="L6" s="165"/>
-      <c r="M6" s="165"/>
-      <c r="N6" s="165"/>
-      <c r="O6" s="165"/>
-      <c r="P6" s="165"/>
-      <c r="Q6" s="165"/>
-      <c r="R6" s="165"/>
-      <c r="S6" s="165"/>
-      <c r="T6" s="165"/>
-      <c r="U6" s="165"/>
-      <c r="V6" s="165"/>
-      <c r="W6" s="165"/>
-      <c r="X6" s="165"/>
-      <c r="Y6" s="165"/>
-      <c r="Z6" s="165"/>
-      <c r="AA6" s="165"/>
-      <c r="AB6" s="165"/>
-      <c r="AC6" s="165"/>
-      <c r="AD6" s="166"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="168"/>
+      <c r="M6" s="168"/>
+      <c r="N6" s="168"/>
+      <c r="O6" s="168"/>
+      <c r="P6" s="168"/>
+      <c r="Q6" s="168"/>
+      <c r="R6" s="168"/>
+      <c r="S6" s="168"/>
+      <c r="T6" s="168"/>
+      <c r="U6" s="168"/>
+      <c r="V6" s="168"/>
+      <c r="W6" s="168"/>
+      <c r="X6" s="168"/>
+      <c r="Y6" s="168"/>
+      <c r="Z6" s="168"/>
+      <c r="AA6" s="168"/>
+      <c r="AB6" s="168"/>
+      <c r="AC6" s="168"/>
+      <c r="AD6" s="169"/>
     </row>
     <row r="7" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="K7" s="164"/>
-      <c r="L7" s="165"/>
-      <c r="M7" s="165"/>
-      <c r="N7" s="165"/>
-      <c r="O7" s="165"/>
-      <c r="P7" s="165"/>
-      <c r="Q7" s="165"/>
-      <c r="R7" s="165"/>
-      <c r="S7" s="165"/>
-      <c r="T7" s="165"/>
-      <c r="U7" s="165"/>
-      <c r="V7" s="165"/>
-      <c r="W7" s="165"/>
-      <c r="X7" s="165"/>
-      <c r="Y7" s="165"/>
-      <c r="Z7" s="165"/>
-      <c r="AA7" s="165"/>
-      <c r="AB7" s="165"/>
-      <c r="AC7" s="165"/>
-      <c r="AD7" s="166"/>
+      <c r="K7" s="167"/>
+      <c r="L7" s="168"/>
+      <c r="M7" s="168"/>
+      <c r="N7" s="168"/>
+      <c r="O7" s="168"/>
+      <c r="P7" s="168"/>
+      <c r="Q7" s="168"/>
+      <c r="R7" s="168"/>
+      <c r="S7" s="168"/>
+      <c r="T7" s="168"/>
+      <c r="U7" s="168"/>
+      <c r="V7" s="168"/>
+      <c r="W7" s="168"/>
+      <c r="X7" s="168"/>
+      <c r="Y7" s="168"/>
+      <c r="Z7" s="168"/>
+      <c r="AA7" s="168"/>
+      <c r="AB7" s="168"/>
+      <c r="AC7" s="168"/>
+      <c r="AD7" s="169"/>
     </row>
     <row r="8" spans="5:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K8" s="164"/>
-      <c r="L8" s="165"/>
-      <c r="M8" s="165"/>
-      <c r="N8" s="165"/>
-      <c r="O8" s="165"/>
-      <c r="P8" s="165"/>
-      <c r="Q8" s="165"/>
-      <c r="R8" s="165"/>
-      <c r="S8" s="165"/>
-      <c r="T8" s="165"/>
-      <c r="U8" s="165"/>
-      <c r="V8" s="165"/>
-      <c r="W8" s="165"/>
-      <c r="X8" s="165"/>
-      <c r="Y8" s="165"/>
-      <c r="Z8" s="165"/>
-      <c r="AA8" s="165"/>
-      <c r="AB8" s="165"/>
-      <c r="AC8" s="165"/>
-      <c r="AD8" s="166"/>
+      <c r="K8" s="167"/>
+      <c r="L8" s="168"/>
+      <c r="M8" s="168"/>
+      <c r="N8" s="168"/>
+      <c r="O8" s="168"/>
+      <c r="P8" s="168"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="168"/>
+      <c r="S8" s="168"/>
+      <c r="T8" s="168"/>
+      <c r="U8" s="168"/>
+      <c r="V8" s="168"/>
+      <c r="W8" s="168"/>
+      <c r="X8" s="168"/>
+      <c r="Y8" s="168"/>
+      <c r="Z8" s="168"/>
+      <c r="AA8" s="168"/>
+      <c r="AB8" s="168"/>
+      <c r="AC8" s="168"/>
+      <c r="AD8" s="169"/>
     </row>
     <row r="9" spans="5:38" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K9" s="167"/>
-      <c r="L9" s="168"/>
-      <c r="M9" s="168"/>
-      <c r="N9" s="168"/>
-      <c r="O9" s="168"/>
-      <c r="P9" s="168"/>
-      <c r="Q9" s="168"/>
-      <c r="R9" s="168"/>
-      <c r="S9" s="168"/>
-      <c r="T9" s="168"/>
-      <c r="U9" s="168"/>
-      <c r="V9" s="168"/>
-      <c r="W9" s="168"/>
-      <c r="X9" s="168"/>
-      <c r="Y9" s="168"/>
-      <c r="Z9" s="168"/>
-      <c r="AA9" s="168"/>
-      <c r="AB9" s="168"/>
-      <c r="AC9" s="168"/>
-      <c r="AD9" s="169"/>
+      <c r="K9" s="170"/>
+      <c r="L9" s="171"/>
+      <c r="M9" s="171"/>
+      <c r="N9" s="171"/>
+      <c r="O9" s="171"/>
+      <c r="P9" s="171"/>
+      <c r="Q9" s="171"/>
+      <c r="R9" s="171"/>
+      <c r="S9" s="171"/>
+      <c r="T9" s="171"/>
+      <c r="U9" s="171"/>
+      <c r="V9" s="171"/>
+      <c r="W9" s="171"/>
+      <c r="X9" s="171"/>
+      <c r="Y9" s="171"/>
+      <c r="Z9" s="171"/>
+      <c r="AA9" s="171"/>
+      <c r="AB9" s="171"/>
+      <c r="AC9" s="171"/>
+      <c r="AD9" s="172"/>
     </row>
     <row r="12" spans="5:38" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
     </row>
     <row r="13" spans="5:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="55"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="56"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="56"/>
-      <c r="Y13" s="56"/>
-      <c r="Z13" s="56"/>
-      <c r="AA13" s="56"/>
-      <c r="AB13" s="56"/>
-      <c r="AC13" s="56"/>
-      <c r="AD13" s="56"/>
-      <c r="AE13" s="56"/>
-      <c r="AF13" s="56"/>
-      <c r="AG13" s="56"/>
-      <c r="AH13" s="56"/>
-      <c r="AI13" s="56"/>
-      <c r="AJ13" s="56"/>
-      <c r="AK13" s="56"/>
-      <c r="AL13" s="57"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="59"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="59"/>
+      <c r="P13" s="59"/>
+      <c r="Q13" s="59"/>
+      <c r="R13" s="59"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="59"/>
+      <c r="U13" s="59"/>
+      <c r="V13" s="59"/>
+      <c r="W13" s="59"/>
+      <c r="X13" s="59"/>
+      <c r="Y13" s="59"/>
+      <c r="Z13" s="59"/>
+      <c r="AA13" s="59"/>
+      <c r="AB13" s="59"/>
+      <c r="AC13" s="59"/>
+      <c r="AD13" s="59"/>
+      <c r="AE13" s="59"/>
+      <c r="AF13" s="59"/>
+      <c r="AG13" s="59"/>
+      <c r="AH13" s="59"/>
+      <c r="AI13" s="59"/>
+      <c r="AJ13" s="59"/>
+      <c r="AK13" s="59"/>
+      <c r="AL13" s="60"/>
     </row>
     <row r="14" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E14" s="58"/>
-      <c r="AL14" s="59"/>
+      <c r="E14" s="61"/>
+      <c r="AL14" s="62"/>
     </row>
     <row r="15" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E15" s="58"/>
-      <c r="AL15" s="59"/>
+      <c r="E15" s="61"/>
+      <c r="AL15" s="62"/>
     </row>
     <row r="16" spans="5:38" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E16" s="58"/>
-      <c r="AL16" s="59"/>
+      <c r="E16" s="61"/>
+      <c r="AL16" s="62"/>
     </row>
     <row r="17" spans="5:71" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="58"/>
-      <c r="H17" s="174" t="s">
-        <v>230</v>
-      </c>
-      <c r="I17" s="175"/>
-      <c r="J17" s="175"/>
-      <c r="K17" s="175"/>
-      <c r="L17" s="175"/>
-      <c r="M17" s="175"/>
-      <c r="N17" s="176"/>
-      <c r="Q17" s="174" t="s">
-        <v>231</v>
-      </c>
-      <c r="R17" s="175"/>
-      <c r="S17" s="175"/>
-      <c r="T17" s="175"/>
-      <c r="U17" s="175"/>
-      <c r="V17" s="176"/>
-      <c r="AL17" s="59"/>
+      <c r="E17" s="61"/>
+      <c r="H17" s="177" t="s">
+        <v>268</v>
+      </c>
+      <c r="I17" s="178"/>
+      <c r="J17" s="178"/>
+      <c r="K17" s="178"/>
+      <c r="L17" s="178"/>
+      <c r="M17" s="178"/>
+      <c r="N17" s="179"/>
+      <c r="Q17" s="177" t="s">
+        <v>269</v>
+      </c>
+      <c r="R17" s="178"/>
+      <c r="S17" s="178"/>
+      <c r="T17" s="178"/>
+      <c r="U17" s="178"/>
+      <c r="V17" s="179"/>
+      <c r="AL17" s="62"/>
     </row>
     <row r="18" spans="5:71" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E18" s="58"/>
-      <c r="H18" s="177"/>
-      <c r="I18" s="178"/>
-      <c r="J18" s="178"/>
-      <c r="K18" s="178"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="178"/>
-      <c r="N18" s="179"/>
-      <c r="Q18" s="177"/>
-      <c r="R18" s="178"/>
-      <c r="S18" s="178"/>
-      <c r="T18" s="178"/>
-      <c r="U18" s="178"/>
-      <c r="V18" s="179"/>
-      <c r="AL18" s="59"/>
-      <c r="BO18" s="132" t="s">
-        <v>226</v>
-      </c>
-      <c r="BP18" s="133"/>
-      <c r="BQ18" s="133"/>
-      <c r="BR18" s="160"/>
-      <c r="BS18" s="35"/>
+      <c r="E18" s="61"/>
+      <c r="H18" s="180"/>
+      <c r="I18" s="181"/>
+      <c r="J18" s="181"/>
+      <c r="K18" s="181"/>
+      <c r="L18" s="181"/>
+      <c r="M18" s="181"/>
+      <c r="N18" s="182"/>
+      <c r="Q18" s="180"/>
+      <c r="R18" s="181"/>
+      <c r="S18" s="181"/>
+      <c r="T18" s="181"/>
+      <c r="U18" s="181"/>
+      <c r="V18" s="182"/>
+      <c r="AL18" s="62"/>
+      <c r="BO18" s="152" t="s">
+        <v>264</v>
+      </c>
+      <c r="BP18" s="153"/>
+      <c r="BQ18" s="153"/>
+      <c r="BR18" s="205"/>
+      <c r="BS18" s="38"/>
     </row>
     <row r="19" spans="5:71" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="E19" s="58"/>
-      <c r="H19" s="180" t="str">
+      <c r="E19" s="61"/>
+      <c r="H19" s="183" t="str">
         <f>INDEX(BP40:BP42,MATCH(MAX(BT40:BT42),BT40:BT42,0))</f>
         <v>Vendor B</v>
       </c>
-      <c r="I19" s="181"/>
-      <c r="J19" s="181"/>
-      <c r="K19" s="181"/>
-      <c r="L19" s="181"/>
-      <c r="M19" s="181"/>
-      <c r="N19" s="182"/>
-      <c r="Q19" s="192" t="str">
+      <c r="I19" s="184"/>
+      <c r="J19" s="184"/>
+      <c r="K19" s="184"/>
+      <c r="L19" s="184"/>
+      <c r="M19" s="184"/>
+      <c r="N19" s="185"/>
+      <c r="Q19" s="195" t="str">
         <f>BP30</f>
         <v>K-1-PUTIH</v>
       </c>
-      <c r="R19" s="193"/>
-      <c r="S19" s="189" t="str">
+      <c r="R19" s="196"/>
+      <c r="S19" s="192" t="str">
         <f>BP31</f>
         <v>K-1-HITAM</v>
       </c>
-      <c r="T19" s="191"/>
-      <c r="U19" s="189" t="str">
+      <c r="T19" s="194"/>
+      <c r="U19" s="192" t="str">
         <f>BP32</f>
         <v>K-1-ABU-ABU</v>
       </c>
-      <c r="V19" s="190"/>
-      <c r="AL19" s="59"/>
-      <c r="BO19" s="70" t="s">
+      <c r="V19" s="193"/>
+      <c r="AL19" s="62"/>
+      <c r="BO19" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="BP19" s="70"/>
+      <c r="BP19" s="84"/>
       <c r="BQ19" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR19" s="49" t="s">
-        <v>67</v>
+        <v>98</v>
+      </c>
+      <c r="BR19" s="52" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E20" s="58"/>
-      <c r="H20" s="183"/>
-      <c r="I20" s="184"/>
-      <c r="J20" s="184"/>
-      <c r="K20" s="184"/>
-      <c r="L20" s="184"/>
-      <c r="M20" s="184"/>
-      <c r="N20" s="185"/>
-      <c r="Q20" s="154">
+      <c r="E20" s="61"/>
+      <c r="H20" s="186"/>
+      <c r="I20" s="187"/>
+      <c r="J20" s="187"/>
+      <c r="K20" s="187"/>
+      <c r="L20" s="187"/>
+      <c r="M20" s="187"/>
+      <c r="N20" s="188"/>
+      <c r="Q20" s="201">
         <f>BQ30</f>
         <v>57</v>
       </c>
-      <c r="R20" s="155"/>
-      <c r="S20" s="155">
+      <c r="R20" s="197"/>
+      <c r="S20" s="197">
         <f>BQ31</f>
         <v>90</v>
       </c>
-      <c r="T20" s="155"/>
-      <c r="U20" s="155">
+      <c r="T20" s="197"/>
+      <c r="U20" s="197">
         <f>BQ32</f>
         <v>98</v>
       </c>
-      <c r="V20" s="194"/>
-      <c r="AL20" s="59"/>
-      <c r="BO20" s="173" t="s">
+      <c r="V20" s="198"/>
+      <c r="AL20" s="62"/>
+      <c r="BO20" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="BP20" s="173"/>
+      <c r="BP20" s="176"/>
       <c r="BQ20" s="22">
         <f>'ADMINISTRASI DEFECT'!N7</f>
         <v>2</v>
@@ -10602,25 +11238,25 @@
       </c>
     </row>
     <row r="21" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E21" s="58"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="184"/>
-      <c r="J21" s="184"/>
-      <c r="K21" s="184"/>
-      <c r="L21" s="184"/>
-      <c r="M21" s="184"/>
-      <c r="N21" s="185"/>
-      <c r="Q21" s="154"/>
-      <c r="R21" s="155"/>
-      <c r="S21" s="155"/>
-      <c r="T21" s="155"/>
-      <c r="U21" s="155"/>
-      <c r="V21" s="194"/>
-      <c r="AL21" s="59"/>
-      <c r="BO21" s="173" t="s">
+      <c r="E21" s="61"/>
+      <c r="H21" s="186"/>
+      <c r="I21" s="187"/>
+      <c r="J21" s="187"/>
+      <c r="K21" s="187"/>
+      <c r="L21" s="187"/>
+      <c r="M21" s="187"/>
+      <c r="N21" s="188"/>
+      <c r="Q21" s="201"/>
+      <c r="R21" s="197"/>
+      <c r="S21" s="197"/>
+      <c r="T21" s="197"/>
+      <c r="U21" s="197"/>
+      <c r="V21" s="198"/>
+      <c r="AL21" s="62"/>
+      <c r="BO21" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="BP21" s="173"/>
+      <c r="BP21" s="176"/>
       <c r="BQ21" s="22">
         <f>'ADMINISTRASI DEFECT'!N8</f>
         <v>1</v>
@@ -10631,26 +11267,26 @@
       </c>
     </row>
     <row r="22" spans="5:71" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E22" s="58"/>
-      <c r="H22" s="186"/>
-      <c r="I22" s="187"/>
-      <c r="J22" s="187"/>
-      <c r="K22" s="187"/>
-      <c r="L22" s="187"/>
-      <c r="M22" s="187"/>
-      <c r="N22" s="188"/>
-      <c r="Q22" s="156"/>
-      <c r="R22" s="157"/>
-      <c r="S22" s="157"/>
-      <c r="T22" s="157"/>
-      <c r="U22" s="157"/>
-      <c r="V22" s="195"/>
-      <c r="AL22" s="59"/>
-      <c r="BO22" s="173" t="s">
+      <c r="E22" s="61"/>
+      <c r="H22" s="189"/>
+      <c r="I22" s="190"/>
+      <c r="J22" s="190"/>
+      <c r="K22" s="190"/>
+      <c r="L22" s="190"/>
+      <c r="M22" s="190"/>
+      <c r="N22" s="191"/>
+      <c r="Q22" s="202"/>
+      <c r="R22" s="199"/>
+      <c r="S22" s="199"/>
+      <c r="T22" s="199"/>
+      <c r="U22" s="199"/>
+      <c r="V22" s="200"/>
+      <c r="AL22" s="62"/>
+      <c r="BO22" s="176" t="s">
         <v>13</v>
       </c>
-      <c r="BP22" s="173"/>
-      <c r="BQ22" s="50">
+      <c r="BP22" s="176"/>
+      <c r="BQ22" s="53">
         <f>'ADMINISTRASI DEFECT'!N9</f>
         <v>0</v>
       </c>
@@ -10660,50 +11296,50 @@
       </c>
     </row>
     <row r="23" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E23" s="58"/>
-      <c r="AL23" s="59"/>
+      <c r="E23" s="61"/>
+      <c r="AL23" s="62"/>
     </row>
     <row r="24" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E24" s="58"/>
-      <c r="AL24" s="59"/>
+      <c r="E24" s="61"/>
+      <c r="AL24" s="62"/>
     </row>
     <row r="25" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E25" s="58"/>
-      <c r="AL25" s="59"/>
+      <c r="E25" s="61"/>
+      <c r="AL25" s="62"/>
     </row>
     <row r="26" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E26" s="58"/>
-      <c r="AL26" s="59"/>
+      <c r="E26" s="61"/>
+      <c r="AL26" s="62"/>
     </row>
     <row r="27" spans="5:71" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E27" s="58"/>
-      <c r="AL27" s="59"/>
+      <c r="E27" s="61"/>
+      <c r="AL27" s="62"/>
     </row>
     <row r="28" spans="5:71" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E28" s="58"/>
-      <c r="AL28" s="59"/>
-      <c r="BP28" s="158" t="s">
-        <v>227</v>
-      </c>
-      <c r="BQ28" s="159"/>
-      <c r="BR28" s="160"/>
+      <c r="E28" s="61"/>
+      <c r="AL28" s="62"/>
+      <c r="BP28" s="203" t="s">
+        <v>265</v>
+      </c>
+      <c r="BQ28" s="204"/>
+      <c r="BR28" s="205"/>
     </row>
     <row r="29" spans="5:71" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="E29" s="58"/>
-      <c r="AL29" s="59"/>
-      <c r="BP29" s="49" t="s">
+      <c r="E29" s="61"/>
+      <c r="AL29" s="62"/>
+      <c r="BP29" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="BQ29" s="49" t="s">
+      <c r="BQ29" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="BR29" s="49" t="s">
+      <c r="BR29" s="52" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E30" s="58"/>
-      <c r="AL30" s="59"/>
+      <c r="E30" s="61"/>
+      <c r="AL30" s="62"/>
       <c r="BP30" s="22" t="str">
         <f>'IMPLEMENTASI FIFO'!K8</f>
         <v>K-1-PUTIH</v>
@@ -10718,8 +11354,8 @@
       </c>
     </row>
     <row r="31" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E31" s="58"/>
-      <c r="AL31" s="59"/>
+      <c r="E31" s="61"/>
+      <c r="AL31" s="62"/>
       <c r="BP31" s="22" t="str">
         <f>'IMPLEMENTASI FIFO'!K9</f>
         <v>K-1-HITAM</v>
@@ -10734,8 +11370,8 @@
       </c>
     </row>
     <row r="32" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E32" s="58"/>
-      <c r="AL32" s="59"/>
+      <c r="E32" s="61"/>
+      <c r="AL32" s="62"/>
       <c r="BP32" s="22" t="str">
         <f>'IMPLEMENTASI FIFO'!K10</f>
         <v>K-1-ABU-ABU</v>
@@ -10750,79 +11386,79 @@
       </c>
     </row>
     <row r="33" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E33" s="58"/>
-      <c r="AL33" s="59"/>
+      <c r="E33" s="61"/>
+      <c r="AL33" s="62"/>
     </row>
     <row r="34" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E34" s="58"/>
-      <c r="AL34" s="59"/>
+      <c r="E34" s="61"/>
+      <c r="AL34" s="62"/>
     </row>
     <row r="35" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E35" s="58"/>
-      <c r="AL35" s="59"/>
+      <c r="E35" s="61"/>
+      <c r="AL35" s="62"/>
     </row>
     <row r="36" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E36" s="58"/>
-      <c r="AL36" s="59"/>
+      <c r="E36" s="61"/>
+      <c r="AL36" s="62"/>
     </row>
     <row r="37" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E37" s="58"/>
-      <c r="AL37" s="59"/>
+      <c r="E37" s="61"/>
+      <c r="AL37" s="62"/>
     </row>
     <row r="38" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E38" s="58"/>
-      <c r="AL38" s="59"/>
-      <c r="BP38" s="158" t="s">
-        <v>225</v>
-      </c>
-      <c r="BQ38" s="159"/>
-      <c r="BR38" s="159"/>
-      <c r="BS38" s="159"/>
-      <c r="BT38" s="159"/>
-      <c r="BU38" s="160"/>
+      <c r="E38" s="61"/>
+      <c r="AL38" s="62"/>
+      <c r="BP38" s="203" t="s">
+        <v>263</v>
+      </c>
+      <c r="BQ38" s="204"/>
+      <c r="BR38" s="204"/>
+      <c r="BS38" s="204"/>
+      <c r="BT38" s="204"/>
+      <c r="BU38" s="205"/>
     </row>
     <row r="39" spans="5:73" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="E39" s="58"/>
-      <c r="AL39" s="59"/>
-      <c r="BP39" s="49" t="s">
+      <c r="E39" s="61"/>
+      <c r="AL39" s="62"/>
+      <c r="BP39" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="BQ39" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="BR39" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="BS39" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="BT39" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="BU39" s="49" t="s">
-        <v>64</v>
+      <c r="BQ39" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BR39" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="BS39" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="BT39" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="BU39" s="52" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E40" s="58"/>
-      <c r="AL40" s="59"/>
+      <c r="E40" s="61"/>
+      <c r="AL40" s="62"/>
       <c r="BP40" s="22" t="str">
         <f>'IMPLEMENTASI VPI'!D23</f>
         <v>Vendor A</v>
       </c>
-      <c r="BQ40" s="26">
+      <c r="BQ40" s="29">
         <f>'IMPLEMENTASI VPI'!E23</f>
         <v>50</v>
       </c>
-      <c r="BR40" s="26">
+      <c r="BR40" s="29">
         <f>'IMPLEMENTASI VPI'!F23</f>
         <v>100</v>
       </c>
-      <c r="BS40" s="26">
+      <c r="BS40" s="29">
         <f>'IMPLEMENTASI VPI'!G23</f>
         <v>96</v>
       </c>
-      <c r="BT40" s="26">
+      <c r="BT40" s="29">
         <f>'IMPLEMENTASI VPI'!H23</f>
         <v>74.2</v>
       </c>
@@ -10832,25 +11468,25 @@
       </c>
     </row>
     <row r="41" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E41" s="58"/>
-      <c r="AL41" s="59"/>
+      <c r="E41" s="61"/>
+      <c r="AL41" s="62"/>
       <c r="BP41" s="22" t="str">
         <f>'IMPLEMENTASI VPI'!D24</f>
         <v>Vendor B</v>
       </c>
-      <c r="BQ41" s="26">
+      <c r="BQ41" s="29">
         <f>'IMPLEMENTASI VPI'!E24</f>
         <v>100</v>
       </c>
-      <c r="BR41" s="26">
+      <c r="BR41" s="29">
         <f>'IMPLEMENTASI VPI'!F24</f>
         <v>100</v>
       </c>
-      <c r="BS41" s="26">
+      <c r="BS41" s="29">
         <f>'IMPLEMENTASI VPI'!G24</f>
         <v>98.630136986301366</v>
       </c>
-      <c r="BT41" s="26">
+      <c r="BT41" s="29">
         <f>'IMPLEMENTASI VPI'!H24</f>
         <v>99.726027397260282</v>
       </c>
@@ -10860,25 +11496,25 @@
       </c>
     </row>
     <row r="42" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E42" s="58"/>
-      <c r="AL42" s="59"/>
+      <c r="E42" s="61"/>
+      <c r="AL42" s="62"/>
       <c r="BP42" s="22" t="str">
         <f>'IMPLEMENTASI VPI'!D25</f>
         <v>Vendor C</v>
       </c>
-      <c r="BQ42" s="26">
+      <c r="BQ42" s="29">
         <f>'IMPLEMENTASI VPI'!E25</f>
         <v>0</v>
       </c>
-      <c r="BR42" s="26">
+      <c r="BR42" s="29">
         <f>'IMPLEMENTASI VPI'!F25</f>
         <v>0</v>
       </c>
-      <c r="BS42" s="26">
+      <c r="BS42" s="29">
         <f>'IMPLEMENTASI VPI'!G25</f>
         <v>100</v>
       </c>
-      <c r="BT42" s="26">
+      <c r="BT42" s="29">
         <f>'IMPLEMENTASI VPI'!H25</f>
         <v>20</v>
       </c>
@@ -10888,432 +11524,430 @@
       </c>
     </row>
     <row r="43" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E43" s="58"/>
-      <c r="AL43" s="59"/>
+      <c r="E43" s="61"/>
+      <c r="AL43" s="62"/>
     </row>
     <row r="44" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E44" s="58"/>
-      <c r="AL44" s="59"/>
+      <c r="E44" s="61"/>
+      <c r="AL44" s="62"/>
     </row>
     <row r="45" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E45" s="58"/>
-      <c r="AL45" s="59"/>
+      <c r="E45" s="61"/>
+      <c r="AL45" s="62"/>
     </row>
     <row r="46" spans="5:73" x14ac:dyDescent="0.25">
-      <c r="E46" s="58"/>
-      <c r="AL46" s="59"/>
+      <c r="E46" s="61"/>
+      <c r="AL46" s="62"/>
     </row>
     <row r="47" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E47" s="58"/>
-      <c r="AL47" s="59"/>
+      <c r="E47" s="61"/>
+      <c r="AL47" s="62"/>
     </row>
     <row r="48" spans="5:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E48" s="58"/>
-      <c r="AL48" s="59"/>
-      <c r="BP48" s="170" t="s">
-        <v>229</v>
-      </c>
-      <c r="BQ48" s="171"/>
-      <c r="BR48" s="171"/>
-      <c r="BS48" s="172"/>
-      <c r="BT48" s="52"/>
+      <c r="E48" s="61"/>
+      <c r="AL48" s="62"/>
+      <c r="BP48" s="173" t="s">
+        <v>267</v>
+      </c>
+      <c r="BQ48" s="174"/>
+      <c r="BR48" s="174"/>
+      <c r="BS48" s="175"/>
+      <c r="BT48" s="55"/>
     </row>
     <row r="49" spans="5:71" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="E49" s="58"/>
-      <c r="AL49" s="59"/>
-      <c r="BP49" s="53" t="s">
+      <c r="E49" s="61"/>
+      <c r="AL49" s="62"/>
+      <c r="BP49" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="BQ49" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="BR49" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="BS49" s="53" t="s">
-        <v>224</v>
+      <c r="BQ49" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="BR49" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="BS49" s="56" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="50" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E50" s="58"/>
-      <c r="AL50" s="59"/>
-      <c r="BP50" s="54" t="str">
+      <c r="E50" s="61"/>
+      <c r="AL50" s="62"/>
+      <c r="BP50" s="57" t="str">
         <f>'ADMINISTRASI DEFECT'!B7</f>
         <v>Vendor A</v>
       </c>
-      <c r="BQ50" s="54">
+      <c r="BQ50" s="57">
         <f>'ADMINISTRASI DEFECT'!D7</f>
         <v>2</v>
       </c>
-      <c r="BR50" s="54">
+      <c r="BR50" s="57">
         <f>'ADMINISTRASI DEFECT'!G7</f>
         <v>1</v>
       </c>
-      <c r="BS50" s="54">
+      <c r="BS50" s="57">
         <f>'ADMINISTRASI DEFECT'!H7</f>
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E51" s="58"/>
-      <c r="AL51" s="59"/>
-      <c r="BP51" s="54" t="str">
+      <c r="E51" s="61"/>
+      <c r="AL51" s="62"/>
+      <c r="BP51" s="57" t="str">
         <f>'ADMINISTRASI DEFECT'!B8</f>
         <v>Vendor B</v>
       </c>
-      <c r="BQ51" s="54">
+      <c r="BQ51" s="57">
         <f>'ADMINISTRASI DEFECT'!D8</f>
         <v>2</v>
       </c>
-      <c r="BR51" s="54">
+      <c r="BR51" s="57">
         <f>'ADMINISTRASI DEFECT'!G8</f>
         <v>2</v>
       </c>
-      <c r="BS51" s="54">
+      <c r="BS51" s="57">
         <f>'ADMINISTRASI DEFECT'!H8</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E52" s="58"/>
-      <c r="AL52" s="59"/>
-      <c r="BP52" s="54" t="str">
+      <c r="E52" s="61"/>
+      <c r="AL52" s="62"/>
+      <c r="BP52" s="57" t="str">
         <f>'ADMINISTRASI DEFECT'!B9</f>
         <v>Vendor C</v>
       </c>
-      <c r="BQ52" s="54">
+      <c r="BQ52" s="57">
         <f>'ADMINISTRASI DEFECT'!D9</f>
         <v>2</v>
       </c>
-      <c r="BR52" s="54">
+      <c r="BR52" s="57">
         <f>'ADMINISTRASI DEFECT'!G9</f>
         <v>0</v>
       </c>
-      <c r="BS52" s="54">
+      <c r="BS52" s="57">
         <f>'ADMINISTRASI DEFECT'!H9</f>
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E53" s="58"/>
-      <c r="AL53" s="59"/>
+      <c r="E53" s="61"/>
+      <c r="AL53" s="62"/>
     </row>
     <row r="54" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E54" s="58"/>
-      <c r="AL54" s="59"/>
+      <c r="E54" s="61"/>
+      <c r="AL54" s="62"/>
     </row>
     <row r="55" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E55" s="58"/>
-      <c r="AL55" s="59"/>
+      <c r="E55" s="61"/>
+      <c r="AL55" s="62"/>
     </row>
     <row r="56" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E56" s="58"/>
-      <c r="AL56" s="59"/>
+      <c r="E56" s="61"/>
+      <c r="AL56" s="62"/>
     </row>
     <row r="57" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E57" s="58"/>
-      <c r="AL57" s="59"/>
+      <c r="E57" s="61"/>
+      <c r="AL57" s="62"/>
     </row>
     <row r="58" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E58" s="58"/>
-      <c r="AL58" s="59"/>
+      <c r="E58" s="61"/>
+      <c r="AL58" s="62"/>
     </row>
     <row r="59" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E59" s="58"/>
-      <c r="AL59" s="59"/>
+      <c r="E59" s="61"/>
+      <c r="AL59" s="62"/>
     </row>
     <row r="60" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E60" s="58"/>
-      <c r="AL60" s="59"/>
+      <c r="E60" s="61"/>
+      <c r="AL60" s="62"/>
     </row>
     <row r="61" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E61" s="58"/>
-      <c r="AL61" s="59"/>
+      <c r="E61" s="61"/>
+      <c r="AL61" s="62"/>
     </row>
     <row r="62" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E62" s="58"/>
-      <c r="AL62" s="59"/>
+      <c r="E62" s="61"/>
+      <c r="AL62" s="62"/>
     </row>
     <row r="63" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E63" s="58"/>
-      <c r="AL63" s="59"/>
+      <c r="E63" s="61"/>
+      <c r="AL63" s="62"/>
     </row>
     <row r="64" spans="5:71" x14ac:dyDescent="0.25">
-      <c r="E64" s="58"/>
-      <c r="AL64" s="59"/>
+      <c r="E64" s="61"/>
+      <c r="AL64" s="62"/>
     </row>
     <row r="65" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E65" s="58"/>
-      <c r="AL65" s="59"/>
+      <c r="E65" s="61"/>
+      <c r="AL65" s="62"/>
     </row>
     <row r="66" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E66" s="58"/>
-      <c r="AL66" s="59"/>
+      <c r="E66" s="61"/>
+      <c r="AL66" s="62"/>
     </row>
     <row r="67" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E67" s="58"/>
-      <c r="AL67" s="59"/>
+      <c r="E67" s="61"/>
+      <c r="AL67" s="62"/>
     </row>
     <row r="68" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E68" s="58"/>
-      <c r="AL68" s="59"/>
+      <c r="E68" s="61"/>
+      <c r="AL68" s="62"/>
     </row>
     <row r="69" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E69" s="58"/>
-      <c r="AL69" s="59"/>
+      <c r="E69" s="61"/>
+      <c r="AL69" s="62"/>
     </row>
     <row r="70" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E70" s="58"/>
-      <c r="AL70" s="59"/>
+      <c r="E70" s="61"/>
+      <c r="AL70" s="62"/>
     </row>
     <row r="71" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E71" s="58"/>
-      <c r="AL71" s="59"/>
+      <c r="E71" s="61"/>
+      <c r="AL71" s="62"/>
     </row>
     <row r="72" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E72" s="58"/>
-      <c r="AL72" s="59"/>
+      <c r="E72" s="61"/>
+      <c r="AL72" s="62"/>
     </row>
     <row r="73" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E73" s="58"/>
-      <c r="AL73" s="59"/>
+      <c r="E73" s="61"/>
+      <c r="AL73" s="62"/>
     </row>
     <row r="74" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E74" s="58"/>
-      <c r="AL74" s="59"/>
+      <c r="E74" s="61"/>
+      <c r="AL74" s="62"/>
     </row>
     <row r="75" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E75" s="58"/>
-      <c r="AL75" s="59"/>
+      <c r="E75" s="61"/>
+      <c r="AL75" s="62"/>
     </row>
     <row r="76" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E76" s="58"/>
-      <c r="AL76" s="59"/>
+      <c r="E76" s="61"/>
+      <c r="AL76" s="62"/>
     </row>
     <row r="77" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E77" s="58"/>
-      <c r="AL77" s="59"/>
+      <c r="E77" s="61"/>
+      <c r="AL77" s="62"/>
     </row>
     <row r="78" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E78" s="58"/>
-      <c r="AL78" s="59"/>
+      <c r="E78" s="61"/>
+      <c r="AL78" s="62"/>
     </row>
     <row r="79" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E79" s="58"/>
-      <c r="AL79" s="59"/>
+      <c r="E79" s="61"/>
+      <c r="AL79" s="62"/>
     </row>
     <row r="80" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E80" s="58"/>
-      <c r="AL80" s="59"/>
+      <c r="E80" s="61"/>
+      <c r="AL80" s="62"/>
     </row>
     <row r="81" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E81" s="58"/>
-      <c r="AL81" s="59"/>
+      <c r="E81" s="61"/>
+      <c r="AL81" s="62"/>
     </row>
     <row r="82" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E82" s="58"/>
-      <c r="AL82" s="59"/>
+      <c r="E82" s="61"/>
+      <c r="AL82" s="62"/>
     </row>
     <row r="83" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E83" s="58"/>
-      <c r="AL83" s="59"/>
+      <c r="E83" s="61"/>
+      <c r="AL83" s="62"/>
     </row>
     <row r="84" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E84" s="58"/>
-      <c r="AL84" s="59"/>
+      <c r="E84" s="61"/>
+      <c r="AL84" s="62"/>
     </row>
     <row r="85" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E85" s="58"/>
-      <c r="AL85" s="59"/>
+      <c r="E85" s="61"/>
+      <c r="AL85" s="62"/>
     </row>
     <row r="86" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E86" s="58"/>
-      <c r="AL86" s="59"/>
+      <c r="E86" s="61"/>
+      <c r="AL86" s="62"/>
     </row>
     <row r="87" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E87" s="58"/>
-      <c r="AL87" s="59"/>
+      <c r="E87" s="61"/>
+      <c r="AL87" s="62"/>
     </row>
     <row r="88" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E88" s="58"/>
-      <c r="AL88" s="59"/>
+      <c r="E88" s="61"/>
+      <c r="AL88" s="62"/>
     </row>
     <row r="89" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E89" s="58"/>
-      <c r="AL89" s="59"/>
+      <c r="E89" s="61"/>
+      <c r="AL89" s="62"/>
     </row>
     <row r="90" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E90" s="58"/>
-      <c r="AL90" s="59"/>
+      <c r="E90" s="61"/>
+      <c r="AL90" s="62"/>
     </row>
     <row r="91" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E91" s="58"/>
-      <c r="AL91" s="59"/>
+      <c r="E91" s="61"/>
+      <c r="AL91" s="62"/>
     </row>
     <row r="92" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E92" s="58"/>
-      <c r="AL92" s="59"/>
+      <c r="E92" s="61"/>
+      <c r="AL92" s="62"/>
     </row>
     <row r="93" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E93" s="58"/>
-      <c r="AL93" s="59"/>
+      <c r="E93" s="61"/>
+      <c r="AL93" s="62"/>
     </row>
     <row r="94" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E94" s="58"/>
-      <c r="AL94" s="59"/>
+      <c r="E94" s="61"/>
+      <c r="AL94" s="62"/>
     </row>
     <row r="95" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E95" s="58"/>
-      <c r="AL95" s="59"/>
+      <c r="E95" s="61"/>
+      <c r="AL95" s="62"/>
     </row>
     <row r="96" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E96" s="58"/>
-      <c r="AL96" s="59"/>
+      <c r="E96" s="61"/>
+      <c r="AL96" s="62"/>
     </row>
     <row r="97" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E97" s="58"/>
-      <c r="AL97" s="59"/>
+      <c r="E97" s="61"/>
+      <c r="AL97" s="62"/>
     </row>
     <row r="98" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E98" s="58"/>
-      <c r="AL98" s="59"/>
+      <c r="E98" s="61"/>
+      <c r="AL98" s="62"/>
     </row>
     <row r="99" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E99" s="58"/>
-      <c r="AL99" s="59"/>
+      <c r="E99" s="61"/>
+      <c r="AL99" s="62"/>
     </row>
     <row r="100" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E100" s="58"/>
-      <c r="AL100" s="59"/>
+      <c r="E100" s="61"/>
+      <c r="AL100" s="62"/>
     </row>
     <row r="101" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E101" s="58"/>
-      <c r="AL101" s="59"/>
+      <c r="E101" s="61"/>
+      <c r="AL101" s="62"/>
     </row>
     <row r="102" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E102" s="58"/>
-      <c r="AL102" s="59"/>
+      <c r="E102" s="61"/>
+      <c r="AL102" s="62"/>
     </row>
     <row r="103" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E103" s="58"/>
-      <c r="AL103" s="59"/>
+      <c r="E103" s="61"/>
+      <c r="AL103" s="62"/>
     </row>
     <row r="104" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E104" s="58"/>
-      <c r="AL104" s="59"/>
+      <c r="E104" s="61"/>
+      <c r="AL104" s="62"/>
     </row>
     <row r="105" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E105" s="58"/>
-      <c r="AL105" s="59"/>
+      <c r="E105" s="61"/>
+      <c r="AL105" s="62"/>
     </row>
     <row r="106" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E106" s="58"/>
-      <c r="AL106" s="59"/>
+      <c r="E106" s="61"/>
+      <c r="AL106" s="62"/>
     </row>
     <row r="107" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E107" s="58"/>
-      <c r="AL107" s="59"/>
+      <c r="E107" s="61"/>
+      <c r="AL107" s="62"/>
     </row>
     <row r="108" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E108" s="58"/>
-      <c r="AL108" s="59"/>
+      <c r="E108" s="61"/>
+      <c r="AL108" s="62"/>
     </row>
     <row r="109" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E109" s="58"/>
-      <c r="AL109" s="59"/>
+      <c r="E109" s="61"/>
+      <c r="AL109" s="62"/>
     </row>
     <row r="110" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E110" s="58"/>
-      <c r="AL110" s="59"/>
+      <c r="E110" s="61"/>
+      <c r="AL110" s="62"/>
     </row>
     <row r="111" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E111" s="58"/>
-      <c r="AL111" s="59"/>
+      <c r="E111" s="61"/>
+      <c r="AL111" s="62"/>
     </row>
     <row r="112" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E112" s="58"/>
-      <c r="AL112" s="59"/>
+      <c r="E112" s="61"/>
+      <c r="AL112" s="62"/>
     </row>
     <row r="113" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E113" s="58"/>
-      <c r="AL113" s="59"/>
+      <c r="E113" s="61"/>
+      <c r="AL113" s="62"/>
     </row>
     <row r="114" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E114" s="58"/>
-      <c r="AL114" s="59"/>
+      <c r="E114" s="61"/>
+      <c r="AL114" s="62"/>
     </row>
     <row r="115" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E115" s="58"/>
-      <c r="AL115" s="59"/>
+      <c r="E115" s="61"/>
+      <c r="AL115" s="62"/>
     </row>
     <row r="116" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E116" s="58"/>
-      <c r="AL116" s="59"/>
+      <c r="E116" s="61"/>
+      <c r="AL116" s="62"/>
     </row>
     <row r="117" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E117" s="58"/>
-      <c r="AL117" s="59"/>
+      <c r="E117" s="61"/>
+      <c r="AL117" s="62"/>
     </row>
     <row r="118" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E118" s="58"/>
-      <c r="AL118" s="59"/>
+      <c r="E118" s="61"/>
+      <c r="AL118" s="62"/>
     </row>
     <row r="119" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E119" s="58"/>
-      <c r="AL119" s="59"/>
+      <c r="E119" s="61"/>
+      <c r="AL119" s="62"/>
     </row>
     <row r="120" spans="5:38" x14ac:dyDescent="0.25">
-      <c r="E120" s="58"/>
-      <c r="AL120" s="59"/>
+      <c r="E120" s="61"/>
+      <c r="AL120" s="62"/>
     </row>
     <row r="121" spans="5:38" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E121" s="60"/>
-      <c r="F121" s="61"/>
-      <c r="G121" s="61"/>
-      <c r="H121" s="61"/>
-      <c r="I121" s="61"/>
-      <c r="J121" s="61"/>
-      <c r="K121" s="61"/>
-      <c r="L121" s="61"/>
-      <c r="M121" s="61"/>
-      <c r="N121" s="61"/>
-      <c r="O121" s="61"/>
-      <c r="P121" s="61"/>
-      <c r="Q121" s="61"/>
-      <c r="R121" s="61"/>
-      <c r="S121" s="61"/>
-      <c r="T121" s="61"/>
-      <c r="U121" s="61"/>
-      <c r="V121" s="61"/>
-      <c r="W121" s="61"/>
-      <c r="X121" s="61"/>
-      <c r="Y121" s="61"/>
-      <c r="Z121" s="61"/>
-      <c r="AA121" s="61"/>
-      <c r="AB121" s="61"/>
-      <c r="AC121" s="61"/>
-      <c r="AD121" s="61"/>
-      <c r="AE121" s="61"/>
-      <c r="AF121" s="61"/>
-      <c r="AG121" s="61"/>
-      <c r="AH121" s="61"/>
-      <c r="AI121" s="61"/>
-      <c r="AJ121" s="61"/>
-      <c r="AK121" s="61"/>
-      <c r="AL121" s="62"/>
+      <c r="E121" s="63"/>
+      <c r="F121" s="64"/>
+      <c r="G121" s="64"/>
+      <c r="H121" s="64"/>
+      <c r="I121" s="64"/>
+      <c r="J121" s="64"/>
+      <c r="K121" s="64"/>
+      <c r="L121" s="64"/>
+      <c r="M121" s="64"/>
+      <c r="N121" s="64"/>
+      <c r="O121" s="64"/>
+      <c r="P121" s="64"/>
+      <c r="Q121" s="64"/>
+      <c r="R121" s="64"/>
+      <c r="S121" s="64"/>
+      <c r="T121" s="64"/>
+      <c r="U121" s="64"/>
+      <c r="V121" s="64"/>
+      <c r="W121" s="64"/>
+      <c r="X121" s="64"/>
+      <c r="Y121" s="64"/>
+      <c r="Z121" s="64"/>
+      <c r="AA121" s="64"/>
+      <c r="AB121" s="64"/>
+      <c r="AC121" s="64"/>
+      <c r="AD121" s="64"/>
+      <c r="AE121" s="64"/>
+      <c r="AF121" s="64"/>
+      <c r="AG121" s="64"/>
+      <c r="AH121" s="64"/>
+      <c r="AI121" s="64"/>
+      <c r="AJ121" s="64"/>
+      <c r="AK121" s="64"/>
+      <c r="AL121" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="BP38:BU38"/>
+    <mergeCell ref="BO18:BR18"/>
+    <mergeCell ref="K5:AD9"/>
     <mergeCell ref="BP48:BS48"/>
     <mergeCell ref="BO19:BP19"/>
     <mergeCell ref="BO22:BP22"/>
     <mergeCell ref="BO21:BP21"/>
     <mergeCell ref="BO20:BP20"/>
-    <mergeCell ref="Q20:R22"/>
-    <mergeCell ref="BP28:BR28"/>
-    <mergeCell ref="BP38:BU38"/>
-    <mergeCell ref="BO18:BR18"/>
-    <mergeCell ref="K5:AD9"/>
     <mergeCell ref="Q17:V18"/>
     <mergeCell ref="H19:N22"/>
     <mergeCell ref="H17:N18"/>
@@ -11322,6 +11956,8 @@
     <mergeCell ref="Q19:R19"/>
     <mergeCell ref="U20:V22"/>
     <mergeCell ref="S20:T22"/>
+    <mergeCell ref="Q20:R22"/>
+    <mergeCell ref="BP28:BR28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
